--- a/output/pdf_financials_xlsx/BVA.xlsx
+++ b/output/pdf_financials_xlsx/BVA.xlsx
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3.352988</v>
+        <v>-3.352988</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.244691</v>
+        <v>-3.244691</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>8.837339</v>
+        <v>-8.837339</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.671818</v>
+        <v>-0.671818</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.154075</v>
+        <v>-0.154075</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.693076</v>
+        <v>-1.693076</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.182866</v>
+        <v>-1.182866</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.344202</v>
+        <v>-1.344202</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.016254</v>
+        <v>-1.016254</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.611495</v>
+        <v>-0.611495</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.593073</v>
+        <v>-1.593073</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.428256</v>
+        <v>-1.428256</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.902293</v>
+        <v>-0.902293</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.506833</v>
+        <v>-0.506833</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.387589</v>
+        <v>-0.387589</v>
       </c>
     </row>
     <row r="17">
@@ -1536,49 +1536,49 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3.352988</v>
+        <v>-3.352988</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.244691</v>
+        <v>-3.244691</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>8.837339</v>
+        <v>-8.837339</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.671818</v>
+        <v>-0.671818</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.154075</v>
+        <v>-0.154075</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.693076</v>
+        <v>-1.693076</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.182866</v>
+        <v>-1.182866</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.344202</v>
+        <v>-1.344202</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.016254</v>
+        <v>-1.016254</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.611495</v>
+        <v>-0.611495</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.593073</v>
+        <v>-1.593073</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.428256</v>
+        <v>-1.428256</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.902293</v>
+        <v>-0.902293</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.506833</v>
+        <v>-0.506833</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.387589</v>
+        <v>-0.387589</v>
       </c>
     </row>
     <row r="21">
@@ -1707,49 +1707,49 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3.352988</v>
+        <v>-3.352988</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.244691</v>
+        <v>-3.244691</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>8.837339</v>
+        <v>-8.837339</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.671818</v>
+        <v>-0.671818</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.154075</v>
+        <v>-0.154075</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.693076</v>
+        <v>-1.693076</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.182866</v>
+        <v>-1.182866</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.344202</v>
+        <v>-1.344202</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.016254</v>
+        <v>-1.016254</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.611495</v>
+        <v>-0.611495</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.593073</v>
+        <v>-1.593073</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.428256</v>
+        <v>-1.428256</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.902293</v>
+        <v>-0.902293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.506833</v>
+        <v>-0.506833</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0.387589</v>
+        <v>-0.387589</v>
       </c>
     </row>
     <row r="24">
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>55.883133</v>
+        <v>-55.883133</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>108.156367</v>
+        <v>-108.156367</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>11.477064</v>
+        <v>-11.477064</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>13.43636</v>
+        <v>-13.43636</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1903,16 +1903,16 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>21.16345</v>
+        <v>-21.16345</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>39.428867</v>
+        <v>-39.428867</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>44.806733</v>
+        <v>-44.806733</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>50.8127</v>
+        <v>-50.8127</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>79.65365</v>
+        <v>-79.65365</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -1955,49 +1955,49 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3.352988</v>
+        <v>-3.352988</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.244691</v>
+        <v>-3.244691</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>8.837339</v>
+        <v>-8.837339</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.671818</v>
+        <v>-0.671818</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.154075</v>
+        <v>-0.154075</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.693076</v>
+        <v>-1.693076</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.182866</v>
+        <v>-1.182866</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.344202</v>
+        <v>-1.344202</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.016254</v>
+        <v>-1.016254</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.611495</v>
+        <v>-0.611495</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.593073</v>
+        <v>-1.593073</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.428256</v>
+        <v>-1.428256</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.902293</v>
+        <v>-0.902293</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.506833</v>
+        <v>-0.506833</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.387589</v>
+        <v>-0.387589</v>
       </c>
     </row>
     <row r="28">
@@ -2069,49 +2069,49 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.352988</v>
+        <v>-3.352988</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.244691</v>
+        <v>-3.244691</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>8.837339</v>
+        <v>-8.837339</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.671818</v>
+        <v>-0.671818</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.154075</v>
+        <v>-0.154075</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.693076</v>
+        <v>-1.693076</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.182866</v>
+        <v>-1.182866</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.344202</v>
+        <v>-1.344202</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.016254</v>
+        <v>-1.016254</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.611495</v>
+        <v>-0.611495</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.593073</v>
+        <v>-1.593073</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.428256</v>
+        <v>-1.428256</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.902293</v>
+        <v>-0.902293</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.506833</v>
+        <v>-0.506833</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.387589</v>
+        <v>-0.387589</v>
       </c>
     </row>
     <row r="30">
@@ -2213,49 +2213,49 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5673,52 +5673,52 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.650203</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.212312</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.245269</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.293165</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.922503</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.750811</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.737978</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.073179</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.237726</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.274816</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.255341</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.252759</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.097529</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.961338</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.920933</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.944847</v>
       </c>
     </row>
     <row r="93">
@@ -9516,7 +9516,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10438,7 +10442,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -21554,7 +21562,11 @@
           <t>Share‐based payments reserve</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -22034,7 +22046,11 @@
           <t>Share‐based payments reserve</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E149" s="5" t="n">
         <v>4.650203</v>
       </c>
@@ -32215,13 +32231,13 @@
         </is>
       </c>
       <c r="R259" s="5" t="n">
-        <v>0.902293</v>
+        <v>-0.902293</v>
       </c>
       <c r="S259" s="5" t="n">
-        <v>0.506833</v>
+        <v>-0.506833</v>
       </c>
       <c r="T259" s="5" t="n">
-        <v>0.387589</v>
+        <v>-0.387589</v>
       </c>
     </row>
     <row r="260">
@@ -34560,16 +34576,16 @@
         </is>
       </c>
       <c r="O286" s="5" t="n">
-        <v>0.611495</v>
+        <v>-0.611495</v>
       </c>
       <c r="P286" s="5" t="n">
-        <v>1.593073</v>
+        <v>-1.593073</v>
       </c>
       <c r="Q286" s="5" t="n">
-        <v>1.428256</v>
+        <v>-1.428256</v>
       </c>
       <c r="R286" s="5" t="n">
-        <v>0.902293</v>
+        <v>-0.902293</v>
       </c>
       <c r="S286" t="inlineStr">
         <is>
@@ -35425,31 +35441,31 @@
         </is>
       </c>
       <c r="F296" s="5" t="n">
-        <v>3.352988</v>
+        <v>-3.352988</v>
       </c>
       <c r="G296" s="5" t="n">
-        <v>3.244691</v>
+        <v>-3.244691</v>
       </c>
       <c r="H296" s="5" t="n">
-        <v>8.837339</v>
+        <v>-8.837339</v>
       </c>
       <c r="I296" s="5" t="n">
-        <v>0.671818</v>
+        <v>-0.671818</v>
       </c>
       <c r="J296" s="5" t="n">
-        <v>0.154075</v>
+        <v>-0.154075</v>
       </c>
       <c r="K296" s="5" t="n">
-        <v>1.693076</v>
+        <v>-1.693076</v>
       </c>
       <c r="L296" s="5" t="n">
-        <v>1.182866</v>
+        <v>-1.182866</v>
       </c>
       <c r="M296" s="5" t="n">
-        <v>1.344202</v>
+        <v>-1.344202</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>1.016254</v>
+        <v>-1.016254</v>
       </c>
       <c r="O296" t="inlineStr">
         <is>
@@ -35721,10 +35737,10 @@
         </is>
       </c>
       <c r="J299" s="5" t="n">
-        <v>0.136305</v>
+        <v>-0.136305</v>
       </c>
       <c r="K299" s="5" t="n">
-        <v>1.678346</v>
+        <v>-1.678346</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -35732,10 +35748,10 @@
         </is>
       </c>
       <c r="M299" s="5" t="n">
-        <v>1.352059</v>
+        <v>-1.352059</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>1.016254</v>
+        <v>-1.016254</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -36627,10 +36643,10 @@
         </is>
       </c>
       <c r="F309" s="5" t="n">
-        <v>3.355488</v>
+        <v>-3.355488</v>
       </c>
       <c r="G309" s="5" t="n">
-        <v>3.247191</v>
+        <v>-3.247191</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
@@ -36653,10 +36669,10 @@
         </is>
       </c>
       <c r="L309" s="5" t="n">
-        <v>1.210009</v>
+        <v>-1.210009</v>
       </c>
       <c r="M309" s="5" t="n">
-        <v>1.352059</v>
+        <v>-1.352059</v>
       </c>
       <c r="N309" t="inlineStr">
         <is>
@@ -37688,10 +37704,10 @@
         </is>
       </c>
       <c r="K320" s="5" t="n">
-        <v>1.678346</v>
+        <v>-1.678346</v>
       </c>
       <c r="L320" s="5" t="n">
-        <v>1.210009</v>
+        <v>-1.210009</v>
       </c>
       <c r="M320" t="inlineStr">
         <is>
@@ -39199,13 +39215,13 @@
         </is>
       </c>
       <c r="H336" s="5" t="n">
-        <v>8.863339</v>
+        <v>-8.863339</v>
       </c>
       <c r="I336" s="5" t="n">
-        <v>0.6383180000000001</v>
+        <v>-0.6383180000000001</v>
       </c>
       <c r="J336" s="5" t="n">
-        <v>0.136305</v>
+        <v>-0.136305</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
@@ -40526,10 +40542,10 @@
         </is>
       </c>
       <c r="G350" s="5" t="n">
-        <v>3.244691</v>
+        <v>-3.244691</v>
       </c>
       <c r="H350" s="5" t="n">
-        <v>8.837339</v>
+        <v>-8.837339</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
@@ -40718,10 +40734,10 @@
         </is>
       </c>
       <c r="G352" s="5" t="n">
-        <v>3.247191</v>
+        <v>-3.247191</v>
       </c>
       <c r="H352" s="5" t="n">
-        <v>8.863339</v>
+        <v>-8.863339</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BVA.xlsx
+++ b/output/pdf_financials_xlsx/BVA.xlsx
@@ -1023,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002527</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000133</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1958,10 +1958,10 @@
         <v>-3.352988</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.244691</v>
+        <v>-3.242164</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8.837339</v>
+        <v>-8.837206</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.671818</v>
@@ -2072,10 +2072,10 @@
         <v>-3.352988</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.244691</v>
+        <v>-3.242164</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.837339</v>
+        <v>-8.837206</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.671818</v>
@@ -2359,52 +2359,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.280975</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.692672</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.023949</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.04494</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.006674</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.013463</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.080941</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.196944</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.325729</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.515505</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.712025</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.119806</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.997068</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.007536</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.201651</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.092269</v>
       </c>
     </row>
     <row r="35">
@@ -2469,52 +2469,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.0125</v>
+        <v>1.293475</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.01</v>
+        <v>0.702672</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.0175</v>
+        <v>0.041449</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.044</v>
+        <v>0.08894000000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.036674</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.132365</v>
+        <v>0.145828</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.06</v>
+        <v>0.140941</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.012858</v>
+        <v>0.209802</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1e-06</v>
+        <v>0.32573</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1e-06</v>
+        <v>0.515506</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1e-06</v>
+        <v>0.712026</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1e-06</v>
+        <v>0.119807</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1e-06</v>
+        <v>0.997069</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1e-06</v>
+        <v>0.007537</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1e-06</v>
+        <v>0.201652</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.025</v>
+        <v>1.117269</v>
       </c>
     </row>
     <row r="37">
@@ -3129,52 +3129,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.358382</v>
+        <v>0.077407</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.713153</v>
+        <v>0.020481</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.05404</v>
+        <v>0.030091</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.056414</v>
+        <v>0.011474</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.015183</v>
+        <v>0.008508999999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.021581</v>
+        <v>0.008118</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.09249400000000001</v>
+        <v>0.011553</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.21617</v>
+        <v>0.019226</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.373108</v>
+        <v>0.047379</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.536733</v>
+        <v>0.021228</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.952749</v>
+        <v>0.240724</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.140735</v>
+        <v>0.020929</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.035104</v>
+        <v>0.038036</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.035591</v>
+        <v>0.028055</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.237314</v>
+        <v>0.035663</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.105467</v>
+        <v>0.013198</v>
       </c>
     </row>
     <row r="49">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -34884,7 +34884,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -40336,7 +40336,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">

--- a/output/pdf_financials_xlsx/BVA.xlsx
+++ b/output/pdf_financials_xlsx/BVA.xlsx
@@ -6762,7 +6762,7 @@
         <v>0</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.005479</v>
       </c>
     </row>
     <row r="111">
@@ -7014,19 +7014,19 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0.017244</v>
+        <v>0.035256</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>-0.003394</v>
+        <v>0.012394</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.060811</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.009835</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.045682</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -8231,7 +8231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T357"/>
+  <dimension ref="A1:T358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22428,7 +22428,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -23556,7 +23560,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -24122,21 +24130,13 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Operating Activities</t>
-        </is>
-      </c>
+      <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Notes to the Consolidated Financial Statements 10</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -24172,26 +24172,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L171" s="5" t="n">
-        <v>-1.182866</v>
-      </c>
-      <c r="M171" s="5" t="n">
-        <v>-1.344202</v>
-      </c>
-      <c r="N171" s="5" t="n">
-        <v>-1.016254</v>
-      </c>
-      <c r="O171" s="5" t="n">
-        <v>-0.611495</v>
-      </c>
-      <c r="P171" s="5" t="n">
-        <v>-1.593073</v>
-      </c>
-      <c r="Q171" s="5" t="n">
-        <v>-1.428256</v>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R171" s="5" t="n">
-        <v>-0.902293</v>
+        <v>2.4e-05</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -24212,15 +24224,19 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -24231,41 +24247,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G172" s="5" t="n">
-        <v>1.725961</v>
-      </c>
-      <c r="H172" s="5" t="n">
-        <v>8.138277</v>
-      </c>
-      <c r="I172" s="5" t="n">
-        <v>0.396105</v>
-      </c>
-      <c r="J172" s="5" t="n">
-        <v>0.08268300000000001</v>
-      </c>
-      <c r="K172" s="5" t="n">
-        <v>0.245872</v>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L172" s="5" t="n">
-        <v>0.143314</v>
+        <v>-1.182866</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>0.289817</v>
+        <v>-1.344202</v>
       </c>
       <c r="N172" s="5" t="n">
-        <v>0.205563</v>
+        <v>-1.016254</v>
       </c>
       <c r="O172" s="5" t="n">
-        <v>0.086003</v>
+        <v>-0.611495</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.173078</v>
+        <v>-1.593073</v>
       </c>
       <c r="Q172" s="5" t="n">
-        <v>0.098159</v>
+        <v>-1.428256</v>
       </c>
       <c r="R172" s="5" t="n">
-        <v>0.122247</v>
+        <v>-0.902293</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -24291,14 +24317,10 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Impairment of mineral properties</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -24309,47 +24331,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G173" s="5" t="n">
+        <v>1.725961</v>
       </c>
       <c r="H173" s="5" t="n">
-        <v>0.000993</v>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.138277</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>0.396105</v>
       </c>
       <c r="J173" s="5" t="n">
-        <v>0.051735</v>
+        <v>0.08268300000000001</v>
       </c>
       <c r="K173" s="5" t="n">
-        <v>0.245053</v>
+        <v>0.245872</v>
       </c>
       <c r="L173" s="5" t="n">
-        <v>0.403414</v>
+        <v>0.143314</v>
       </c>
       <c r="M173" s="5" t="n">
-        <v>0.106772</v>
+        <v>0.289817</v>
       </c>
       <c r="N173" s="5" t="n">
-        <v>0.042488</v>
+        <v>0.205563</v>
       </c>
       <c r="O173" s="5" t="n">
-        <v>0.003279</v>
+        <v>0.086003</v>
       </c>
       <c r="P173" s="5" t="n">
-        <v>0.298171</v>
+        <v>0.173078</v>
       </c>
       <c r="Q173" s="5" t="n">
-        <v>0.261325</v>
-      </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.098159</v>
+      </c>
+      <c r="R173" s="5" t="n">
+        <v>0.122247</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -24375,53 +24391,65 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Items not involving cash total</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F174" s="5" t="n">
-        <v>-2.216492</v>
-      </c>
-      <c r="G174" s="5" t="n">
-        <v>-1.404643</v>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H174" s="5" t="n">
-        <v>-0.659076</v>
-      </c>
-      <c r="I174" s="5" t="n">
-        <v>-0.261332</v>
+        <v>0.000993</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J174" s="5" t="n">
-        <v>-0.136951</v>
+        <v>0.051735</v>
       </c>
       <c r="K174" s="5" t="n">
-        <v>-0.314143</v>
+        <v>0.245053</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>-0.60973</v>
+        <v>0.403414</v>
       </c>
       <c r="M174" s="5" t="n">
-        <v>-0.9698830000000001</v>
+        <v>0.106772</v>
       </c>
       <c r="N174" s="5" t="n">
-        <v>-0.767772</v>
+        <v>0.042488</v>
       </c>
       <c r="O174" s="5" t="n">
-        <v>-0.5270629999999999</v>
+        <v>0.003279</v>
       </c>
       <c r="P174" s="5" t="n">
-        <v>-1.138113</v>
+        <v>0.298171</v>
       </c>
       <c r="Q174" s="5" t="n">
-        <v>-1.08279</v>
-      </c>
-      <c r="R174" s="5" t="n">
-        <v>-0.772038</v>
+        <v>0.261325</v>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -24442,66 +24470,58 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Receivables</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Items not involving cash total</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F175" s="5" t="n">
+        <v>-2.216492</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>-1.404643</v>
       </c>
       <c r="H175" s="5" t="n">
-        <v>0.007325</v>
+        <v>-0.659076</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>0.002595</v>
+        <v>-0.261332</v>
       </c>
       <c r="J175" s="5" t="n">
-        <v>-0.004979</v>
+        <v>-0.136951</v>
       </c>
       <c r="K175" s="5" t="n">
-        <v>-0.021111</v>
+        <v>-0.314143</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>0.026462</v>
+        <v>-0.60973</v>
       </c>
       <c r="M175" s="5" t="n">
-        <v>0.001336</v>
+        <v>-0.9698830000000001</v>
       </c>
       <c r="N175" s="5" t="n">
-        <v>-0.006319</v>
+        <v>-0.767772</v>
       </c>
       <c r="O175" s="5" t="n">
-        <v>0.002174</v>
+        <v>-0.5270629999999999</v>
       </c>
       <c r="P175" s="5" t="n">
-        <v>0.000808</v>
+        <v>-1.138113</v>
       </c>
       <c r="Q175" s="5" t="n">
-        <v>-9.399999999999999e-05</v>
+        <v>-1.08279</v>
       </c>
       <c r="R175" s="5" t="n">
-        <v>0.000243</v>
+        <v>-0.772038</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -24527,12 +24547,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Receivables</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -24551,37 +24571,37 @@
         </is>
       </c>
       <c r="H176" s="5" t="n">
-        <v>0.018617</v>
+        <v>0.007325</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>0.002965</v>
+        <v>0.002595</v>
       </c>
       <c r="J176" s="5" t="n">
-        <v>0.000391</v>
+        <v>-0.004979</v>
       </c>
       <c r="K176" s="5" t="n">
-        <v>-0.003435</v>
+        <v>-0.021111</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>-0.007673</v>
+        <v>0.026462</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>-0.028153</v>
+        <v>0.001336</v>
       </c>
       <c r="N176" s="5" t="n">
-        <v>0.026151</v>
+        <v>-0.006319</v>
       </c>
       <c r="O176" s="5" t="n">
-        <v>-0.003236</v>
+        <v>0.002174</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.003535</v>
+        <v>0.000808</v>
       </c>
       <c r="Q176" s="5" t="n">
-        <v>-0.017107</v>
+        <v>-9.399999999999999e-05</v>
       </c>
       <c r="R176" s="5" t="n">
-        <v>0.009981</v>
+        <v>0.000243</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -24607,12 +24627,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -24631,37 +24651,37 @@
         </is>
       </c>
       <c r="H177" s="5" t="n">
-        <v>0.057292</v>
+        <v>0.018617</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>0.120195</v>
+        <v>0.002965</v>
       </c>
       <c r="J177" s="5" t="n">
-        <v>0.086092</v>
+        <v>0.000391</v>
       </c>
       <c r="K177" s="5" t="n">
-        <v>-0.057876</v>
+        <v>-0.003435</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>0.03216</v>
+        <v>-0.007673</v>
       </c>
       <c r="M177" s="5" t="n">
-        <v>-0.087643</v>
+        <v>-0.028153</v>
       </c>
       <c r="N177" s="5" t="n">
-        <v>0.09145300000000001</v>
+        <v>0.026151</v>
       </c>
       <c r="O177" s="5" t="n">
-        <v>-0.143961</v>
+        <v>-0.003236</v>
       </c>
       <c r="P177" s="5" t="n">
-        <v>-0.041309</v>
+        <v>0.003535</v>
       </c>
       <c r="Q177" s="5" t="n">
-        <v>0.101513</v>
+        <v>-0.017107</v>
       </c>
       <c r="R177" s="5" t="n">
-        <v>-0.09066399999999999</v>
+        <v>0.009981</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -24687,10 +24707,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Due to related parties</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -24707,37 +24731,37 @@
         </is>
       </c>
       <c r="H178" s="5" t="n">
-        <v>0.477917</v>
+        <v>0.057292</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>0.08079</v>
+        <v>0.120195</v>
       </c>
       <c r="J178" s="5" t="n">
-        <v>0.188969</v>
+        <v>0.086092</v>
       </c>
       <c r="K178" s="5" t="n">
-        <v>-0.114134</v>
+        <v>-0.057876</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>0.045489</v>
+        <v>0.03216</v>
       </c>
       <c r="M178" s="5" t="n">
-        <v>-0.068228</v>
+        <v>-0.087643</v>
       </c>
       <c r="N178" s="5" t="n">
-        <v>0.172706</v>
+        <v>0.09145300000000001</v>
       </c>
       <c r="O178" s="5" t="n">
-        <v>0.023967</v>
+        <v>-0.143961</v>
       </c>
       <c r="P178" s="5" t="n">
-        <v>-0.174056</v>
+        <v>-0.041309</v>
       </c>
       <c r="Q178" s="5" t="n">
-        <v>0.04072</v>
+        <v>0.101513</v>
       </c>
       <c r="R178" s="5" t="n">
-        <v>0.059608</v>
+        <v>-0.09066399999999999</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -24763,14 +24787,10 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items total</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
+          <t>Due to related parties</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -24787,37 +24807,37 @@
         </is>
       </c>
       <c r="H179" s="5" t="n">
-        <v>0.561151</v>
+        <v>0.477917</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>0.206545</v>
+        <v>0.08079</v>
       </c>
       <c r="J179" s="5" t="n">
-        <v>0.270473</v>
+        <v>0.188969</v>
       </c>
       <c r="K179" s="5" t="n">
-        <v>-0.196556</v>
+        <v>-0.114134</v>
       </c>
       <c r="L179" s="5" t="n">
-        <v>0.096438</v>
+        <v>0.045489</v>
       </c>
       <c r="M179" s="5" t="n">
-        <v>-0.182688</v>
+        <v>-0.068228</v>
       </c>
       <c r="N179" s="5" t="n">
-        <v>0.283991</v>
+        <v>0.172706</v>
       </c>
       <c r="O179" s="5" t="n">
-        <v>-0.121056</v>
+        <v>0.023967</v>
       </c>
       <c r="P179" s="5" t="n">
-        <v>-0.211022</v>
+        <v>-0.174056</v>
       </c>
       <c r="Q179" s="5" t="n">
-        <v>0.125032</v>
+        <v>0.04072</v>
       </c>
       <c r="R179" s="5" t="n">
-        <v>-0.020832</v>
+        <v>0.059608</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -24843,12 +24863,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cash Used In Operating Activities</t>
+          <t>Change in non-cash working capital items total</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -24866,44 +24886,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H180" s="5" t="n">
+        <v>0.561151</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>0.206545</v>
+      </c>
+      <c r="J180" s="5" t="n">
+        <v>0.270473</v>
       </c>
       <c r="K180" s="5" t="n">
-        <v>-0.510699</v>
+        <v>-0.196556</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>-0.513292</v>
+        <v>0.096438</v>
       </c>
       <c r="M180" s="5" t="n">
-        <v>-1.152571</v>
+        <v>-0.182688</v>
       </c>
       <c r="N180" s="5" t="n">
-        <v>-0.483781</v>
+        <v>0.283991</v>
       </c>
       <c r="O180" s="5" t="n">
-        <v>-0.648119</v>
+        <v>-0.121056</v>
       </c>
       <c r="P180" s="5" t="n">
-        <v>-1.349135</v>
+        <v>-0.211022</v>
       </c>
       <c r="Q180" s="5" t="n">
-        <v>-0.957758</v>
+        <v>0.125032</v>
       </c>
       <c r="R180" s="5" t="n">
-        <v>-0.79287</v>
+        <v>-0.020832</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -24924,15 +24938,19 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Mineral property acquisition costs, net</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Cash Used In Operating Activities</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -24953,35 +24971,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I181" s="5" t="n">
-        <v>-0.113897</v>
-      </c>
-      <c r="J181" s="5" t="n">
-        <v>-0.134195</v>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K181" s="5" t="n">
-        <v>-0.19436</v>
+        <v>-0.510699</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>-0.143314</v>
+        <v>-0.513292</v>
       </c>
       <c r="M181" s="5" t="n">
-        <v>-0.177459</v>
+        <v>-1.152571</v>
       </c>
       <c r="N181" s="5" t="n">
-        <v>-0.205563</v>
+        <v>-0.483781</v>
       </c>
       <c r="O181" s="5" t="n">
-        <v>-0.149271</v>
+        <v>-0.648119</v>
       </c>
       <c r="P181" s="5" t="n">
-        <v>-0.162535</v>
+        <v>-1.349135</v>
       </c>
       <c r="Q181" s="5" t="n">
-        <v>-0.157448</v>
+        <v>-0.957758</v>
       </c>
       <c r="R181" s="5" t="n">
-        <v>-0.212243</v>
+        <v>-0.79287</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -25007,7 +25029,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Reclamation bonds</t>
+          <t>Mineral property acquisition costs, net</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -25031,39 +25053,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I182" s="5" t="n">
+        <v>-0.113897</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>0.004851</v>
+        <v>-0.134195</v>
       </c>
       <c r="K182" s="5" t="n">
-        <v>0.025717</v>
+        <v>-0.19436</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>-0.003705</v>
+        <v>-0.143314</v>
       </c>
       <c r="M182" s="5" t="n">
-        <v>0.07020899999999999</v>
+        <v>-0.177459</v>
       </c>
       <c r="N182" s="5" t="n">
-        <v>-0.016982</v>
+        <v>-0.205563</v>
       </c>
       <c r="O182" s="5" t="n">
-        <v>0.04501</v>
+        <v>-0.149271</v>
       </c>
       <c r="P182" s="5" t="n">
-        <v>0.004935</v>
+        <v>-0.162535</v>
       </c>
       <c r="Q182" s="5" t="n">
-        <v>-0.00138</v>
-      </c>
-      <c r="R182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.157448</v>
+      </c>
+      <c r="R182" s="5" t="n">
+        <v>-0.212243</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -25089,14 +25107,10 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Cash Used in Investing Activities</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Reclamation bonds</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -25112,42 +25126,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H183" s="5" t="n">
-        <v>-0.19841</v>
-      </c>
-      <c r="I183" s="5" t="n">
-        <v>-0.078641</v>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J183" s="5" t="n">
-        <v>-0.127775</v>
+        <v>0.004851</v>
       </c>
       <c r="K183" s="5" t="n">
-        <v>-0.172832</v>
+        <v>0.025717</v>
       </c>
       <c r="L183" s="5" t="n">
-        <v>-0.137184</v>
+        <v>-0.003705</v>
       </c>
       <c r="M183" s="5" t="n">
-        <v>-0.061568</v>
+        <v>0.07020899999999999</v>
       </c>
       <c r="N183" s="5" t="n">
-        <v>-0.222545</v>
-      </c>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.016982</v>
+      </c>
+      <c r="O183" s="5" t="n">
+        <v>0.04501</v>
+      </c>
+      <c r="P183" s="5" t="n">
+        <v>0.004935</v>
       </c>
       <c r="Q183" s="5" t="n">
-        <v>-0.158828</v>
-      </c>
-      <c r="R183" s="5" t="n">
-        <v>-0.212243</v>
+        <v>-0.00138</v>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -25168,17 +25184,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares, net</t>
+          <t>Cash Used in Investing Activities</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -25196,40 +25212,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H184" s="5" t="n">
+        <v>-0.19841</v>
+      </c>
+      <c r="I184" s="5" t="n">
+        <v>-0.078641</v>
+      </c>
+      <c r="J184" s="5" t="n">
+        <v>-0.127775</v>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>-0.172832</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>-0.137184</v>
+      </c>
+      <c r="M184" s="5" t="n">
+        <v>-0.061568</v>
+      </c>
+      <c r="N184" s="5" t="n">
+        <v>-0.222545</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -25242,10 +25244,10 @@
         </is>
       </c>
       <c r="Q184" s="5" t="n">
-        <v>1.983213</v>
+        <v>-0.158828</v>
       </c>
       <c r="R184" s="5" t="n">
-        <v>0.02725</v>
+        <v>-0.212243</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
@@ -25271,10 +25273,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Cash Provided by Financing Activity</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>Proceeds from issuance of shares, net</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -25365,14 +25371,10 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Foreign Exchange Effect on Cash</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>EffectOfExchangeRateChanges</t>
-        </is>
-      </c>
+          <t>Cash Provided by Financing Activity</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -25434,10 +25436,10 @@
         </is>
       </c>
       <c r="Q186" s="5" t="n">
-        <v>0.010635</v>
+        <v>1.983213</v>
       </c>
       <c r="R186" s="5" t="n">
-        <v>-0.011669</v>
+        <v>0.02725</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -25463,10 +25465,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Cash During the Year</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>Foreign Exchange Effect on Cash</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>EffectOfExchangeRateChanges</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -25528,10 +25534,10 @@
         </is>
       </c>
       <c r="Q187" s="5" t="n">
-        <v>0.877262</v>
+        <v>0.010635</v>
       </c>
       <c r="R187" s="5" t="n">
-        <v>-0.989532</v>
+        <v>-0.011669</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
@@ -25557,14 +25563,10 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Cash, Beginning of Year</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Increase (Decrease) in Cash During the Year</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -25626,10 +25628,10 @@
         </is>
       </c>
       <c r="Q188" s="5" t="n">
-        <v>0.119806</v>
+        <v>0.877262</v>
       </c>
       <c r="R188" s="5" t="n">
-        <v>0.997068</v>
+        <v>-0.989532</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -25655,12 +25657,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Cash, End of Year $</t>
+          <t>Cash, Beginning of Year</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -25724,10 +25726,10 @@
         </is>
       </c>
       <c r="Q189" s="5" t="n">
+        <v>0.119806</v>
+      </c>
+      <c r="R189" s="5" t="n">
         <v>0.997068</v>
-      </c>
-      <c r="R189" s="5" t="n">
-        <v>0.007536</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
@@ -25748,15 +25750,19 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>present or future value.</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>business. As of July 31, 2023, the Company had a working capital deficit of $722,304 (2022 - working capital of $246,396). The Company incurred a net loss of $902,293 for the year ended July</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Cash, End of Year $</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -25818,10 +25824,10 @@
         </is>
       </c>
       <c r="Q190" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.997068</v>
       </c>
       <c r="R190" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.007536</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -25842,12 +25848,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Inc., incorporated in Nevada, USA.</t>
+          <t>present or future value.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>business. As of July 31, 2023, the Company had a working capital deficit of $722,304 (2022 - working capital of $246,396). The Company incurred a net loss of $902,293 for the year ended July</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -25901,17 +25907,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O191" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="P191" s="5" t="n">
-        <v>0.002022</v>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q191" s="5" t="n">
         <v>0.002023</v>
       </c>
       <c r="R191" s="5" t="n">
-        <v>2.4e-05</v>
+        <v>3.1e-05</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -25932,12 +25942,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Inc., incorporated in Nevada, USA.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Restricted cash</t>
+          <t>November</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -25992,20 +26002,16 @@
         </is>
       </c>
       <c r="O192" s="5" t="n">
-        <v>-0.21626</v>
+        <v>0.002021</v>
       </c>
       <c r="P192" s="5" t="n">
-        <v>0.21626</v>
-      </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002022</v>
+      </c>
+      <c r="Q192" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="R192" s="5" t="n">
+        <v>2.4e-05</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -26031,14 +26037,10 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Cash (Used in) Provided by Investing Activities</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Restricted cash</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -26089,16 +26091,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O193" s="5" t="n">
+        <v>-0.21626</v>
       </c>
       <c r="P193" s="5" t="n">
-        <v>0.05866</v>
-      </c>
-      <c r="Q193" s="5" t="n">
-        <v>-0.158828</v>
+        <v>0.21626</v>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
@@ -26124,17 +26126,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares, net</t>
+          <t>Cash (Used in) Provided by Investing Activities</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -26157,34 +26159,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I194" s="5" t="n">
-        <v>0.097383</v>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K194" s="5" t="n">
-        <v>0.729239</v>
-      </c>
-      <c r="L194" s="5" t="n">
-        <v>0.784785</v>
-      </c>
-      <c r="M194" s="5" t="n">
-        <v>1.335139</v>
-      </c>
-      <c r="N194" s="5" t="n">
-        <v>0.897832</v>
-      </c>
-      <c r="O194" s="5" t="n">
-        <v>0.94585</v>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P194" s="5" t="n">
-        <v>0.7904910000000001</v>
+        <v>0.05866</v>
       </c>
       <c r="Q194" s="5" t="n">
-        <v>1.983213</v>
+        <v>-0.158828</v>
       </c>
       <c r="R194" t="inlineStr">
         <is>
@@ -26215,10 +26229,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Subscriptions received</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Proceeds from issuance of shares, net</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -26239,48 +26257,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I195" s="5" t="n">
+        <v>0.097383</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K195" s="5" t="n">
+        <v>0.729239</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>0.784785</v>
+      </c>
+      <c r="M195" s="5" t="n">
+        <v>1.335139</v>
+      </c>
+      <c r="N195" s="5" t="n">
+        <v>0.897832</v>
+      </c>
+      <c r="O195" s="5" t="n">
+        <v>0.94585</v>
       </c>
       <c r="P195" s="5" t="n">
-        <v>0.1085</v>
-      </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.7904910000000001</v>
+      </c>
+      <c r="Q195" s="5" t="n">
+        <v>1.983213</v>
       </c>
       <c r="R195" t="inlineStr">
         <is>
@@ -26311,7 +26315,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Advances from exploration partners</t>
+          <t>Subscriptions received</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -26365,11 +26369,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O196" s="5" t="n">
-        <v>0.21626</v>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P196" s="5" t="n">
-        <v>-0.21626</v>
+        <v>0.1085</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -26405,56 +26411,70 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Cash Provided by Financing Activities</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Advances from exploration partners</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F197" s="5" t="n">
-        <v>3.017428</v>
-      </c>
-      <c r="G197" s="5" t="n">
-        <v>0.911381</v>
-      </c>
-      <c r="H197" s="5" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="I197" s="5" t="n">
-        <v>0.097383</v>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K197" s="5" t="n">
-        <v>0.729239</v>
-      </c>
-      <c r="L197" s="5" t="n">
-        <v>0.784785</v>
-      </c>
-      <c r="M197" s="5" t="n">
-        <v>1.335139</v>
-      </c>
-      <c r="N197" s="5" t="n">
-        <v>0.897832</v>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O197" s="5" t="n">
-        <v>1.16211</v>
+        <v>0.21626</v>
       </c>
       <c r="P197" s="5" t="n">
-        <v>0.682731</v>
-      </c>
-      <c r="Q197" s="5" t="n">
-        <v>1.983213</v>
+        <v>-0.21626</v>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
@@ -26485,12 +26505,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Foreign Exchange Effect on Cash</t>
+          <t>Cash Provided by Financing Activities</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>EffectOfExchangeRateChanges</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -26499,40 +26519,42 @@
         </is>
       </c>
       <c r="F198" s="5" t="n">
-        <v>-0.010406</v>
+        <v>3.017428</v>
       </c>
       <c r="G198" s="5" t="n">
-        <v>-0.009606</v>
+        <v>0.911381</v>
       </c>
       <c r="H198" s="5" t="n">
-        <v>0.000697</v>
+        <v>0.285</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>-0.002221</v>
-      </c>
-      <c r="J198" s="5" t="n">
-        <v>0.001042</v>
+        <v>0.097383</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>-6e-05</v>
+        <v>0.729239</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>0.00168</v>
+        <v>0.784785</v>
       </c>
       <c r="M198" s="5" t="n">
-        <v>0.009514999999999999</v>
+        <v>1.335139</v>
       </c>
       <c r="N198" s="5" t="n">
-        <v>-0.00173</v>
+        <v>0.897832</v>
       </c>
       <c r="O198" s="5" t="n">
-        <v>0.00305</v>
+        <v>1.16211</v>
       </c>
       <c r="P198" s="5" t="n">
-        <v>0.015525</v>
+        <v>0.682731</v>
       </c>
       <c r="Q198" s="5" t="n">
-        <v>0.010635</v>
+        <v>1.983213</v>
       </c>
       <c r="R198" t="inlineStr">
         <is>
@@ -26563,66 +26585,54 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Cash During the Year</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>Foreign Exchange Effect on Cash</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>EffectOfExchangeRateChanges</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F199" s="5" t="n">
+        <v>-0.010406</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>-0.009606</v>
+      </c>
+      <c r="H199" s="5" t="n">
+        <v>0.000697</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>-0.038266</v>
+        <v>-0.002221</v>
       </c>
       <c r="J199" s="5" t="n">
-        <v>0.006789</v>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001042</v>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>-6e-05</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>0.00168</v>
+      </c>
+      <c r="M199" s="5" t="n">
+        <v>0.009514999999999999</v>
+      </c>
+      <c r="N199" s="5" t="n">
+        <v>-0.00173</v>
+      </c>
+      <c r="O199" s="5" t="n">
+        <v>0.00305</v>
       </c>
       <c r="P199" s="5" t="n">
-        <v>-0.5922190000000001</v>
+        <v>0.015525</v>
       </c>
       <c r="Q199" s="5" t="n">
-        <v>0.877262</v>
+        <v>0.010635</v>
       </c>
       <c r="R199" t="inlineStr">
         <is>
@@ -26653,54 +26663,66 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Cash, Beginning of Year</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Increase (Decrease) in Cash During the Year</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F200" s="5" t="n">
-        <v>1.280975</v>
-      </c>
-      <c r="G200" s="5" t="n">
-        <v>0.692672</v>
-      </c>
-      <c r="H200" s="5" t="n">
-        <v>0.023949</v>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I200" s="5" t="n">
-        <v>0.04494</v>
+        <v>-0.038266</v>
       </c>
       <c r="J200" s="5" t="n">
-        <v>0.006674</v>
-      </c>
-      <c r="K200" s="5" t="n">
-        <v>0.013463</v>
-      </c>
-      <c r="L200" s="5" t="n">
-        <v>0.059111</v>
-      </c>
-      <c r="M200" s="5" t="n">
-        <v>0.1951</v>
-      </c>
-      <c r="N200" s="5" t="n">
-        <v>0.325729</v>
-      </c>
-      <c r="O200" s="5" t="n">
-        <v>0.515505</v>
+        <v>0.006789</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P200" s="5" t="n">
-        <v>0.712025</v>
+        <v>-0.5922190000000001</v>
       </c>
       <c r="Q200" s="5" t="n">
-        <v>0.119806</v>
+        <v>0.877262</v>
       </c>
       <c r="R200" t="inlineStr">
         <is>
@@ -26731,12 +26753,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Cash, End of Year $</t>
+          <t>Cash, Beginning of Year</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -26745,40 +26767,40 @@
         </is>
       </c>
       <c r="F201" s="5" t="n">
+        <v>1.280975</v>
+      </c>
+      <c r="G201" s="5" t="n">
         <v>0.692672</v>
       </c>
-      <c r="G201" s="5" t="n">
+      <c r="H201" s="5" t="n">
         <v>0.023949</v>
       </c>
-      <c r="H201" s="5" t="n">
+      <c r="I201" s="5" t="n">
         <v>0.04494</v>
       </c>
-      <c r="I201" s="5" t="n">
+      <c r="J201" s="5" t="n">
         <v>0.006674</v>
       </c>
-      <c r="J201" s="5" t="n">
+      <c r="K201" s="5" t="n">
         <v>0.013463</v>
       </c>
-      <c r="K201" s="5" t="n">
-        <v>0.080941</v>
-      </c>
       <c r="L201" s="5" t="n">
-        <v>0.196944</v>
+        <v>0.059111</v>
       </c>
       <c r="M201" s="5" t="n">
+        <v>0.1951</v>
+      </c>
+      <c r="N201" s="5" t="n">
         <v>0.325729</v>
       </c>
-      <c r="N201" s="5" t="n">
+      <c r="O201" s="5" t="n">
         <v>0.515505</v>
       </c>
-      <c r="O201" s="5" t="n">
+      <c r="P201" s="5" t="n">
         <v>0.712025</v>
       </c>
-      <c r="P201" s="5" t="n">
+      <c r="Q201" s="5" t="n">
         <v>0.119806</v>
-      </c>
-      <c r="Q201" s="5" t="n">
-        <v>0.997068</v>
       </c>
       <c r="R201" t="inlineStr">
         <is>
@@ -26804,17 +26826,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Cash Provided by (Used in) Investing Activities</t>
+          <t>Cash, End of Year $</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -26822,61 +26844,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F202" s="5" t="n">
+        <v>0.692672</v>
+      </c>
+      <c r="G202" s="5" t="n">
+        <v>0.023949</v>
+      </c>
+      <c r="H202" s="5" t="n">
+        <v>0.04494</v>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>0.006674</v>
+      </c>
+      <c r="J202" s="5" t="n">
+        <v>0.013463</v>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>0.080941</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>0.196944</v>
+      </c>
+      <c r="M202" s="5" t="n">
+        <v>0.325729</v>
+      </c>
+      <c r="N202" s="5" t="n">
+        <v>0.515505</v>
       </c>
       <c r="O202" s="5" t="n">
-        <v>-0.320521</v>
+        <v>0.712025</v>
       </c>
       <c r="P202" s="5" t="n">
-        <v>0.05866</v>
-      </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.119806</v>
+      </c>
+      <c r="Q202" s="5" t="n">
+        <v>0.997068</v>
       </c>
       <c r="R202" t="inlineStr">
         <is>
@@ -26902,31 +26904,43 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Decrease in Cash During the Year</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Cash Provided by (Used in) Investing Activities</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F203" s="5" t="n">
-        <v>-0.588303</v>
-      </c>
-      <c r="G203" s="5" t="n">
-        <v>-0.668723</v>
-      </c>
-      <c r="H203" s="5" t="n">
-        <v>-0.010638</v>
-      </c>
-      <c r="I203" s="5" t="n">
-        <v>-0.038266</v>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -26954,10 +26968,10 @@
         </is>
       </c>
       <c r="O203" s="5" t="n">
-        <v>0.19652</v>
+        <v>-0.320521</v>
       </c>
       <c r="P203" s="5" t="n">
-        <v>-0.5922190000000001</v>
+        <v>0.05866</v>
       </c>
       <c r="Q203" t="inlineStr">
         <is>
@@ -26988,12 +27002,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Exploration advances</t>
+          <t>Decrease in Cash During the Year</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -27002,25 +27016,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F204" s="5" t="n">
+        <v>-0.588303</v>
+      </c>
+      <c r="G204" s="5" t="n">
+        <v>-0.668723</v>
+      </c>
+      <c r="H204" s="5" t="n">
+        <v>-0.010638</v>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>-0.038266</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -27042,18 +27048,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N204" s="5" t="n">
-        <v>-0.000114</v>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O204" s="5" t="n">
+        <v>0.19652</v>
+      </c>
+      <c r="P204" s="5" t="n">
+        <v>-0.5922190000000001</v>
       </c>
       <c r="Q204" t="inlineStr">
         <is>
@@ -27089,7 +27093,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Realized gain on sale of marketable securities</t>
+          <t>Exploration advances</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -27118,24 +27122,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J205" s="5" t="n">
-        <v>-0.003394</v>
-      </c>
-      <c r="K205" s="5" t="n">
-        <v>-0.016892</v>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M205" s="5" t="n">
-        <v>-0.006396</v>
-      </c>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="5" t="n">
+        <v>-0.000114</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
@@ -27176,12 +27184,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Proceeds from sale of marketable securities</t>
+          <t>Realized gain on sale of marketable securities</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -27205,20 +27213,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I206" s="5" t="n">
-        <v>0.035256</v>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J206" s="5" t="n">
-        <v>0.012394</v>
+        <v>-0.003394</v>
       </c>
       <c r="K206" s="5" t="n">
-        <v>0.060811</v>
-      </c>
-      <c r="L206" s="5" t="n">
-        <v>0.009835</v>
+        <v>-0.016892</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M206" s="5" t="n">
-        <v>0.045682</v>
+        <v>-0.006396</v>
       </c>
       <c r="N206" t="inlineStr">
         <is>
@@ -27264,15 +27276,19 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Increase in Cash During the Year</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
+          <t>Proceeds from sale of marketable securities</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -27293,25 +27309,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I207" s="5" t="n">
+        <v>0.035256</v>
       </c>
       <c r="J207" s="5" t="n">
-        <v>0.006789</v>
+        <v>0.012394</v>
       </c>
       <c r="K207" s="5" t="n">
-        <v>0.045648</v>
+        <v>0.060811</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>0.135989</v>
+        <v>0.009835</v>
       </c>
       <c r="M207" s="5" t="n">
-        <v>0.130515</v>
-      </c>
-      <c r="N207" s="5" t="n">
-        <v>0.189776</v>
+        <v>0.045682</v>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
@@ -27357,7 +27373,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Cash, Held on Behalf of Exploration Partners</t>
+          <t>Increase in Cash During the Year</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -27376,32 +27392,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H208" s="5" t="n">
-        <v>0.031629</v>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J208" s="5" t="n">
+        <v>0.006789</v>
       </c>
       <c r="K208" s="5" t="n">
-        <v>0.02183</v>
+        <v>0.045648</v>
       </c>
       <c r="L208" s="5" t="n">
-        <v>0.001844</v>
+        <v>0.135989</v>
       </c>
       <c r="M208" s="5" t="n">
-        <v>0.000114</v>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.130515</v>
+      </c>
+      <c r="N208" s="5" t="n">
+        <v>0.189776</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -27442,12 +27456,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2.  Basis of Preparation, continued</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>Cash, Held on Behalf of Exploration Partners</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -27466,10 +27480,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H209" s="5" t="n">
+        <v>0.031629</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -27481,21 +27493,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K209" s="5" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>0.001844</v>
       </c>
       <c r="M209" s="5" t="n">
-        <v>0.002019</v>
-      </c>
-      <c r="N209" s="5" t="n">
-        <v>2.5e-05</v>
+        <v>0.000114</v>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -27536,12 +27546,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>2.  Basis of Preparation, continued</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Impairment of marketable securities</t>
+          <t>November</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -27570,24 +27580,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J210" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K210" s="5" t="n">
-        <v>0.050676</v>
-      </c>
-      <c r="L210" s="5" t="n">
-        <v>0.009998999999999999</v>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M210" s="5" t="n">
+        <v>0.002019</v>
+      </c>
+      <c r="N210" s="5" t="n">
+        <v>2.5e-05</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
@@ -27633,7 +27645,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Realized (gain) loss on sale of marketable securities</t>
+          <t>Impairment of marketable securities</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -27662,21 +27674,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J211" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>0.050676</v>
       </c>
       <c r="L211" s="5" t="n">
-        <v>0.007665</v>
-      </c>
-      <c r="M211" s="5" t="n">
-        <v>-0.006396</v>
+        <v>0.009998999999999999</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N211" t="inlineStr">
         <is>
@@ -27722,49 +27732,55 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Realized (gain) loss on sale of marketable securities</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F212" s="5" t="n">
-        <v>-3.352988</v>
-      </c>
-      <c r="G212" s="5" t="n">
-        <v>-3.244691</v>
-      </c>
-      <c r="H212" s="5" t="n">
-        <v>-8.837339</v>
-      </c>
-      <c r="I212" s="5" t="n">
-        <v>-0.671818</v>
-      </c>
-      <c r="J212" s="5" t="n">
-        <v>-0.154075</v>
-      </c>
-      <c r="K212" s="5" t="n">
-        <v>-1.693076</v>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L212" s="5" t="n">
-        <v>-1.182866</v>
-      </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007665</v>
+      </c>
+      <c r="M212" s="5" t="n">
+        <v>-0.006396</v>
       </c>
       <c r="N212" t="inlineStr">
         <is>
@@ -27810,46 +27826,44 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Interest accretion</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F213" s="5" t="n">
+        <v>-3.352988</v>
+      </c>
+      <c r="G213" s="5" t="n">
+        <v>-3.244691</v>
       </c>
       <c r="H213" s="5" t="n">
-        <v>0.041262</v>
+        <v>-8.837339</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>0.007399</v>
+        <v>-0.671818</v>
       </c>
       <c r="J213" s="5" t="n">
-        <v>0.013397</v>
+        <v>-0.154075</v>
       </c>
       <c r="K213" s="5" t="n">
-        <v>0.010267</v>
-      </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.693076</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>-1.182866</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
@@ -27905,7 +27919,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt</t>
+          <t>Interest accretion</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -27924,23 +27938,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H214" s="5" t="n">
+        <v>0.041262</v>
+      </c>
+      <c r="I214" s="5" t="n">
+        <v>0.007399</v>
+      </c>
+      <c r="J214" s="5" t="n">
+        <v>0.013397</v>
       </c>
       <c r="K214" s="5" t="n">
-        <v>0.842776</v>
+        <v>0.010267</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -28001,7 +28009,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Realized loss (gain) on sale of marketable securities</t>
+          <t>Loss on settlement of debt</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -28036,10 +28044,12 @@
         </is>
       </c>
       <c r="K215" s="5" t="n">
-        <v>-0.016892</v>
-      </c>
-      <c r="L215" s="5" t="n">
-        <v>0.007665</v>
+        <v>0.842776</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
@@ -28090,12 +28100,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Loan repayment</t>
+          <t>Realized loss (gain) on sale of marketable securities</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -28124,16 +28134,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J216" s="5" t="n">
-        <v>-0.010825</v>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K216" s="5" t="n">
-        <v>-0.065</v>
-      </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.016892</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>0.007665</v>
       </c>
       <c r="M216" t="inlineStr">
         <is>
@@ -28184,19 +28194,15 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Cash (Used In) Provided By Operating Activities</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Loan repayment</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -28223,10 +28229,10 @@
         </is>
       </c>
       <c r="J217" s="5" t="n">
-        <v>0.133522</v>
+        <v>-0.010825</v>
       </c>
       <c r="K217" s="5" t="n">
-        <v>-0.510699</v>
+        <v>-0.065</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -28282,17 +28288,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Realized (gain) loss on sale of investment</t>
+          <t>Cash (Used In) Provided By Operating Activities</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>SaleOfInvestment</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -28315,16 +28321,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I218" s="5" t="n">
-        <v>0.017244</v>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J218" s="5" t="n">
-        <v>-0.003394</v>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.133522</v>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>-0.510699</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -28380,17 +28386,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Cash Provided By (Used In) Operating Activities</t>
+          <t>Realized (gain) loss on sale of investment</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>SaleOfInvestment</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -28414,10 +28420,10 @@
         </is>
       </c>
       <c r="I219" s="5" t="n">
-        <v>-0.054787</v>
+        <v>0.017244</v>
       </c>
       <c r="J219" s="5" t="n">
-        <v>0.133522</v>
+        <v>-0.003394</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -28478,17 +28484,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Realized loss on sale of investment</t>
+          <t>Cash Provided By (Used In) Operating Activities</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>SaleOfInvestment</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -28512,12 +28518,10 @@
         </is>
       </c>
       <c r="I220" s="5" t="n">
-        <v>0.017244</v>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.054787</v>
+      </c>
+      <c r="J220" s="5" t="n">
+        <v>0.133522</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -28578,17 +28582,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Cash Used in Operating Activities</t>
+          <t>Realized loss on sale of investment</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>SaleOfInvestment</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -28606,11 +28610,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H221" s="5" t="n">
-        <v>-0.097925</v>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I221" s="5" t="n">
-        <v>-0.054787</v>
+        <v>0.017244</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -28676,31 +28682,39 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Mineral property acquisition costs</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr"/>
+          <t>Cash Used in Operating Activities</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F222" s="5" t="n">
-        <v>-0.435016</v>
-      </c>
-      <c r="G222" s="5" t="n">
-        <v>-0.283758</v>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H222" s="5" t="n">
-        <v>-0.19841</v>
+        <v>-0.097925</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>-0.113897</v>
+        <v>-0.054787</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -28771,36 +28785,26 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Proceeds from sale of investment</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>SaleOfInvestment</t>
-        </is>
-      </c>
+          <t>Mineral property acquisition costs</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F223" s="5" t="n">
+        <v>-0.435016</v>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>-0.283758</v>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>-0.19841</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>0.035256</v>
+        <v>-0.113897</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -28866,15 +28870,19 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Loans received</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
+          <t>Proceeds from sale of investment</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -28890,13 +28898,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H224" s="5" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>0.035256</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -28962,32 +28970,32 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Share‐based payments</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Loans received</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F225" s="5" t="n">
-        <v>0.720066</v>
-      </c>
-      <c r="G225" s="5" t="n">
-        <v>0.104481</v>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H225" s="5" t="n">
-        <v>0.000993</v>
+        <v>0.285</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -29058,30 +29066,32 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Interest accretion                                                       41,388                        ‐</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Interest accretion                                                       41,388                        ‐ total</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>Share‐based payments</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F226" s="5" t="n">
+        <v>0.720066</v>
       </c>
       <c r="G226" s="5" t="n">
-        <v>-1.404643</v>
+        <v>0.104481</v>
       </c>
       <c r="H226" s="5" t="n">
-        <v>-0.65895</v>
+        <v>0.000993</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -29152,32 +29162,30 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Change in non‐cash working capital items</t>
+          <t>Interest accretion                                                       41,388                        ‐</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Receivables</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Interest accretion                                                       41,388                        ‐ total</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F227" s="5" t="n">
-        <v>-0.000262</v>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>0.017097</v>
+        <v>-1.404643</v>
       </c>
       <c r="H227" s="5" t="n">
-        <v>0.007325</v>
+        <v>-0.65895</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
@@ -29253,12 +29261,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Receivables</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -29267,13 +29275,13 @@
         </is>
       </c>
       <c r="F228" s="5" t="n">
-        <v>0.060832</v>
+        <v>-0.000262</v>
       </c>
       <c r="G228" s="5" t="n">
-        <v>-0.00961</v>
+        <v>0.017097</v>
       </c>
       <c r="H228" s="5" t="n">
-        <v>0.018617</v>
+        <v>0.007325</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -29349,12 +29357,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -29363,13 +29371,13 @@
         </is>
       </c>
       <c r="F229" s="5" t="n">
-        <v>0.015338</v>
+        <v>0.060832</v>
       </c>
       <c r="G229" s="5" t="n">
-        <v>-0.115262</v>
+        <v>-0.00961</v>
       </c>
       <c r="H229" s="5" t="n">
-        <v>0.057292</v>
+        <v>0.018617</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -29445,23 +29453,27 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Due to related parties</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F230" s="5" t="n">
-        <v>-0.891083</v>
+        <v>0.015338</v>
       </c>
       <c r="G230" s="5" t="n">
-        <v>0.160293</v>
+        <v>-0.115262</v>
       </c>
       <c r="H230" s="5" t="n">
-        <v>0.477917</v>
+        <v>0.057292</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -29537,27 +29549,23 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Change in non‐cash working capital items total</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
+          <t>Due to related parties</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F231" s="5" t="n">
-        <v>-0.815175</v>
+        <v>-0.891083</v>
       </c>
       <c r="G231" s="5" t="n">
-        <v>0.052518</v>
+        <v>0.160293</v>
       </c>
       <c r="H231" s="5" t="n">
-        <v>0.561151</v>
+        <v>0.477917</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -29633,12 +29641,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Cash Used in Operating Activities</t>
+          <t>Change in non‐cash working capital items total</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -29647,13 +29655,13 @@
         </is>
       </c>
       <c r="F232" s="5" t="n">
-        <v>-3.031667</v>
+        <v>-0.815175</v>
       </c>
       <c r="G232" s="5" t="n">
-        <v>-1.352125</v>
+        <v>0.052518</v>
       </c>
       <c r="H232" s="5" t="n">
-        <v>-0.097799</v>
+        <v>0.561151</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -29724,17 +29732,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Reclamation bonds                                                                                     ‐            65,385</t>
+          <t>Change in non‐cash working capital items</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Cash Used in Investing Activities</t>
+          <t>Cash Used in Operating Activities</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -29742,16 +29750,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F233" s="5" t="n">
+        <v>-3.031667</v>
       </c>
       <c r="G233" s="5" t="n">
-        <v>-0.218373</v>
+        <v>-1.352125</v>
       </c>
       <c r="H233" s="5" t="n">
-        <v>-0.19841</v>
+        <v>-0.097799</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -29822,17 +29828,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Interest paid                                                                  (126)                       ‐</t>
+          <t>Reclamation bonds                                                                                     ‐            65,385</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Cash Provided by Financing Activities</t>
+          <t>Cash Used in Investing Activities</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -29846,10 +29852,10 @@
         </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>0.911381</v>
+        <v>-0.218373</v>
       </c>
       <c r="H234" s="5" t="n">
-        <v>0.284874</v>
+        <v>-0.19841</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -29925,12 +29931,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Foreign Exchange Effect on Cash</t>
+          <t>Cash Provided by Financing Activities</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>EffectOfExchangeRateChanges</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -29944,10 +29950,10 @@
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>-0.009606</v>
+        <v>0.911381</v>
       </c>
       <c r="H235" s="5" t="n">
-        <v>0.000697</v>
+        <v>0.284874</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -30023,10 +30029,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Decrease in Cash During the Year</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>Foreign Exchange Effect on Cash</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>EffectOfExchangeRateChanges</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -30038,10 +30048,10 @@
         </is>
       </c>
       <c r="G236" s="5" t="n">
-        <v>-0.668723</v>
+        <v>-0.009606</v>
       </c>
       <c r="H236" s="5" t="n">
-        <v>-0.010638</v>
+        <v>0.000697</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -30117,14 +30127,10 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Cash, Beginning of Year</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Decrease in Cash During the Year</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -30136,10 +30142,10 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>0.692672</v>
+        <v>-0.668723</v>
       </c>
       <c r="H237" s="5" t="n">
-        <v>0.023949</v>
+        <v>-0.010638</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -30215,12 +30221,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Cash, End of Year $</t>
+          <t>Cash, Beginning of Year</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -30234,10 +30240,10 @@
         </is>
       </c>
       <c r="G238" s="5" t="n">
+        <v>0.692672</v>
+      </c>
+      <c r="H238" s="5" t="n">
         <v>0.023949</v>
-      </c>
-      <c r="H238" s="5" t="n">
-        <v>0.04494</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -30308,30 +30314,34 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Interest paid                                                                  (126)                       ‐</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>Cash, End of Year $</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F239" s="5" t="n">
-        <v>0.010406</v>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>0.009606</v>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.023949</v>
+      </c>
+      <c r="H239" s="5" t="n">
+        <v>0.04494</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -30407,7 +30417,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Write‐off of mineral properties</t>
+          <t>Unrealized foreign exchange loss</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -30417,10 +30427,10 @@
         </is>
       </c>
       <c r="F240" s="5" t="n">
-        <v>0.406024</v>
+        <v>0.010406</v>
       </c>
       <c r="G240" s="5" t="n">
-        <v>1.725961</v>
+        <v>0.009606</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -30496,12 +30506,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Cash acquired on Amalgamation                                                                   ‐            23,923</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Reclamation bonds</t>
+          <t>Write‐off of mineral properties</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -30511,10 +30521,10 @@
         </is>
       </c>
       <c r="F241" s="5" t="n">
-        <v>-0.152565</v>
+        <v>0.406024</v>
       </c>
       <c r="G241" s="5" t="n">
-        <v>0.065385</v>
+        <v>1.725961</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -30595,24 +30605,20 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Cash Used in Investing Activities</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Reclamation bonds</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F242" s="5" t="n">
-        <v>-0.563658</v>
+        <v>-0.152565</v>
       </c>
       <c r="G242" s="5" t="n">
-        <v>-0.218373</v>
+        <v>0.065385</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -30688,25 +30694,29 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Cash acquired on Amalgamation                                                                   ‐            23,923</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares, net of issuance costs</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>Cash Used in Investing Activities</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F243" s="5" t="n">
-        <v>3.017428</v>
+        <v>-0.563658</v>
       </c>
       <c r="G243" s="5" t="n">
-        <v>0.911381</v>
+        <v>-0.218373</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -30777,13 +30787,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Financing Activities</t>
+        </is>
+      </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Administration 10</t>
+          <t>Proceeds from issuance of shares, net of issuance costs</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -30792,15 +30806,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F244" s="5" t="n">
+        <v>3.017428</v>
+      </c>
+      <c r="G244" s="5" t="n">
+        <v>0.911381</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -30857,11 +30867,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S244" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="T244" s="5" t="n">
-        <v>0.06</v>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -30873,14 +30887,10 @@
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Consulting 10</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Administration 10</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -30952,10 +30962,10 @@
         </is>
       </c>
       <c r="S245" s="5" t="n">
-        <v>0.118975</v>
+        <v>0.06</v>
       </c>
       <c r="T245" s="5" t="n">
-        <v>0.024645</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="246">
@@ -30967,10 +30977,14 @@
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Exploration and evaluation 9 &amp; 10</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>Consulting 10</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -31042,10 +31056,10 @@
         </is>
       </c>
       <c r="S246" s="5" t="n">
-        <v>0.145647</v>
+        <v>0.118975</v>
       </c>
       <c r="T246" s="5" t="n">
-        <v>0.143745</v>
+        <v>0.024645</v>
       </c>
     </row>
     <row r="247">
@@ -31057,7 +31071,7 @@
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Investor relations and corporate development 10</t>
+          <t>Exploration and evaluation 9 &amp; 10</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -31132,10 +31146,10 @@
         </is>
       </c>
       <c r="S247" s="5" t="n">
-        <v>0.064553</v>
+        <v>0.145647</v>
       </c>
       <c r="T247" s="5" t="n">
-        <v>0.056531</v>
+        <v>0.143745</v>
       </c>
     </row>
     <row r="248">
@@ -31147,14 +31161,10 @@
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Office and general 10</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Investor relations and corporate development 10</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -31226,10 +31236,10 @@
         </is>
       </c>
       <c r="S248" s="5" t="n">
-        <v>0.053553</v>
+        <v>0.064553</v>
       </c>
       <c r="T248" s="5" t="n">
-        <v>0.046505</v>
+        <v>0.056531</v>
       </c>
     </row>
     <row r="249">
@@ -31241,12 +31251,12 @@
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Professional fees 10</t>
+          <t>Office and general 10</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -31320,10 +31330,10 @@
         </is>
       </c>
       <c r="S249" s="5" t="n">
-        <v>0.07355200000000001</v>
+        <v>0.053553</v>
       </c>
       <c r="T249" s="5" t="n">
-        <v>0.098134</v>
+        <v>0.046505</v>
       </c>
     </row>
     <row r="250">
@@ -31335,10 +31345,14 @@
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Regulatory fees and taxes</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>Professional fees 10</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -31404,14 +31418,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R250" s="5" t="n">
-        <v>0.034044</v>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S250" s="5" t="n">
-        <v>0.034797</v>
+        <v>0.07355200000000001</v>
       </c>
       <c r="T250" s="5" t="n">
-        <v>0.022569</v>
+        <v>0.098134</v>
       </c>
     </row>
     <row r="251">
@@ -31423,14 +31439,10 @@
       <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Shareholders' communication</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Regulatory fees and taxes</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -31497,13 +31509,13 @@
         </is>
       </c>
       <c r="R251" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.034044</v>
       </c>
       <c r="S251" s="5" t="n">
-        <v>0.008945</v>
+        <v>0.034797</v>
       </c>
       <c r="T251" s="5" t="n">
-        <v>0.006601</v>
+        <v>0.022569</v>
       </c>
     </row>
     <row r="252">
@@ -31515,12 +31527,12 @@
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
+          <t>Shareholders' communication</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -31589,13 +31601,13 @@
         </is>
       </c>
       <c r="R252" s="5" t="n">
-        <v>0.014828</v>
+        <v>0.0094</v>
       </c>
       <c r="S252" s="5" t="n">
-        <v>0.017664</v>
+        <v>0.008945</v>
       </c>
       <c r="T252" s="5" t="n">
-        <v>0.007564</v>
+        <v>0.006601</v>
       </c>
     </row>
     <row r="253">
@@ -31607,10 +31619,14 @@
       <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Accretion of asset retirement obligation 11</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>Transfer agent</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -31676,18 +31692,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R253" s="5" t="n">
+        <v>0.014828</v>
+      </c>
+      <c r="S253" s="5" t="n">
+        <v>0.017664</v>
       </c>
       <c r="T253" s="5" t="n">
-        <v>0.005479</v>
+        <v>0.007564</v>
       </c>
     </row>
     <row r="254">
@@ -31699,14 +31711,10 @@
       <c r="B254" t="inlineStr"/>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Accretion of asset retirement obligation 11</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -31772,14 +31780,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R254" s="5" t="n">
-        <v>-0.0047</v>
-      </c>
-      <c r="S254" s="5" t="n">
-        <v>0.014191</v>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T254" s="5" t="n">
-        <v>-0.000481</v>
+        <v>0.005479</v>
       </c>
     </row>
     <row r="255">
@@ -31791,10 +31803,14 @@
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Interest on accounts payable</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -31860,16 +31876,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R255" s="5" t="n">
+        <v>-0.0047</v>
       </c>
       <c r="S255" s="5" t="n">
-        <v>0.005055</v>
+        <v>0.014191</v>
       </c>
       <c r="T255" s="5" t="n">
-        <v>0.008489</v>
+        <v>-0.000481</v>
       </c>
     </row>
     <row r="256">
@@ -31881,14 +31895,10 @@
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Other income 9</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Interest on accounts payable</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -31960,10 +31970,10 @@
         </is>
       </c>
       <c r="S256" s="5" t="n">
-        <v>-0.002827</v>
+        <v>0.005055</v>
       </c>
       <c r="T256" s="5" t="n">
-        <v>-0.056799</v>
+        <v>0.008489</v>
       </c>
     </row>
     <row r="257">
@@ -31975,10 +31985,14 @@
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Recovery of mineral properties 9</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
+          <t>Other income 9</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -32050,10 +32064,10 @@
         </is>
       </c>
       <c r="S257" s="5" t="n">
-        <v>-0.087272</v>
+        <v>-0.002827</v>
       </c>
       <c r="T257" s="5" t="n">
-        <v>-0.010394</v>
+        <v>-0.056799</v>
       </c>
     </row>
     <row r="258">
@@ -32065,7 +32079,7 @@
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Unrealized gain on marketable securities 7</t>
+          <t>Recovery of mineral properties 9</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -32139,13 +32153,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S258" s="5" t="n">
+        <v>-0.087272</v>
       </c>
       <c r="T258" s="5" t="n">
-        <v>-0.024999</v>
+        <v>-0.010394</v>
       </c>
     </row>
     <row r="259">
@@ -32157,14 +32169,10 @@
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Unrealized gain on marketable securities 7</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -32230,14 +32238,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R259" s="5" t="n">
-        <v>-0.902293</v>
-      </c>
-      <c r="S259" s="5" t="n">
-        <v>-0.506833</v>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T259" s="5" t="n">
-        <v>-0.387589</v>
+        <v>-0.024999</v>
       </c>
     </row>
     <row r="260">
@@ -32249,12 +32261,12 @@
       <c r="B260" t="inlineStr"/>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted 12</t>
+          <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -32322,20 +32334,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R260" s="5" t="n">
+        <v>-0.902293</v>
+      </c>
+      <c r="S260" s="5" t="n">
+        <v>-0.506833</v>
+      </c>
+      <c r="T260" s="5" t="n">
+        <v>-0.387589</v>
       </c>
     </row>
     <row r="261">
@@ -32344,17 +32350,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Weighted average number of shares outstanding -</t>
-        </is>
-      </c>
+      <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>Loss per share - basic and diluted 12</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -32420,14 +32426,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R261" s="5" t="n">
-        <v>131.27768</v>
-      </c>
-      <c r="S261" s="5" t="n">
-        <v>142.55083</v>
-      </c>
-      <c r="T261" s="5" t="n">
-        <v>153.343622</v>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="262">
@@ -32436,10 +32448,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding -</t>
+        </is>
+      </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Administration 9</t>
+          <t>Weighted average number of shares outstanding - basic and diluted</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -32509,15 +32525,13 @@
         </is>
       </c>
       <c r="R262" s="5" t="n">
-        <v>0.05</v>
+        <v>131.27768</v>
       </c>
       <c r="S262" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="T262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>142.55083</v>
+      </c>
+      <c r="T262" s="5" t="n">
+        <v>153.343622</v>
       </c>
     </row>
     <row r="263">
@@ -32529,14 +32543,10 @@
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Consulting 9</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Administration 9</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -32603,10 +32613,10 @@
         </is>
       </c>
       <c r="R263" s="5" t="n">
-        <v>0.111129</v>
+        <v>0.05</v>
       </c>
       <c r="S263" s="5" t="n">
-        <v>0.118975</v>
+        <v>0.06</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -32623,10 +32633,14 @@
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Exploration and evaluation 8 &amp; 9</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
+          <t>Consulting 9</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -32693,10 +32707,10 @@
         </is>
       </c>
       <c r="R264" s="5" t="n">
-        <v>0.329794</v>
+        <v>0.111129</v>
       </c>
       <c r="S264" s="5" t="n">
-        <v>0.145647</v>
+        <v>0.118975</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -32713,7 +32727,7 @@
       <c r="B265" t="inlineStr"/>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Investor relations and corporate development 9</t>
+          <t>Exploration and evaluation 8 &amp; 9</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -32783,10 +32797,10 @@
         </is>
       </c>
       <c r="R265" s="5" t="n">
-        <v>0.0835</v>
+        <v>0.329794</v>
       </c>
       <c r="S265" s="5" t="n">
-        <v>0.064553</v>
+        <v>0.145647</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -32803,14 +32817,10 @@
       <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Office and general 9</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Investor relations and corporate development 9</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -32877,10 +32887,10 @@
         </is>
       </c>
       <c r="R266" s="5" t="n">
-        <v>0.058611</v>
+        <v>0.0835</v>
       </c>
       <c r="S266" s="5" t="n">
-        <v>0.053553</v>
+        <v>0.064553</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -32897,12 +32907,12 @@
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Professional fees 9</t>
+          <t>Office and general 9</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -32971,10 +32981,10 @@
         </is>
       </c>
       <c r="R267" s="5" t="n">
-        <v>0.072994</v>
+        <v>0.058611</v>
       </c>
       <c r="S267" s="5" t="n">
-        <v>0.07355200000000001</v>
+        <v>0.053553</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -32991,10 +33001,14 @@
       <c r="B268" t="inlineStr"/>
       <c r="C268" t="inlineStr">
         <is>
-          <t>(Recovery) Impairment of mineral properties 8</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
+          <t>Professional fees 9</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -33061,10 +33075,10 @@
         </is>
       </c>
       <c r="R268" s="5" t="n">
-        <v>0.122247</v>
+        <v>0.072994</v>
       </c>
       <c r="S268" s="5" t="n">
-        <v>-0.087272</v>
+        <v>0.07355200000000001</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -33081,7 +33095,7 @@
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Interest on overdue debt</t>
+          <t>(Recovery) Impairment of mineral properties 8</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -33151,10 +33165,10 @@
         </is>
       </c>
       <c r="R269" s="5" t="n">
-        <v>0.020446</v>
+        <v>0.122247</v>
       </c>
       <c r="S269" s="5" t="n">
-        <v>0.005055</v>
+        <v>-0.087272</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -33171,14 +33185,10 @@
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Other income 8</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Interest on overdue debt</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -33244,13 +33254,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R270" s="5" t="n">
+        <v>0.020446</v>
       </c>
       <c r="S270" s="5" t="n">
-        <v>-0.002827</v>
+        <v>0.005055</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -33267,12 +33275,12 @@
       <c r="B271" t="inlineStr"/>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted 11</t>
+          <t>Other income 8</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -33340,13 +33348,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R271" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S271" s="5" t="n">
+        <v>-0.002827</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -33360,27 +33368,31 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
+      <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Administration 9 $</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
+          <t>Loss per share - basic and diluted 11</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F272" s="5" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="G272" s="5" t="n">
-        <v>0.0985</v>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -33397,29 +33409,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K272" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L272" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M272" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N272" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="O272" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="P272" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="Q272" s="5" t="n">
-        <v>0.06</v>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R272" s="5" t="n">
-        <v>0.05</v>
+        <v>1e-08</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -33445,24 +33471,20 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Consulting 9</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Administration 9 $</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F273" s="5" t="n">
-        <v>0.216905</v>
+        <v>0.096</v>
       </c>
       <c r="G273" s="5" t="n">
-        <v>0.172611</v>
+        <v>0.0985</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -33474,32 +33496,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J273" s="5" t="n">
-        <v>0.07275</v>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K273" s="5" t="n">
-        <v>0.028543</v>
+        <v>0.06</v>
       </c>
       <c r="L273" s="5" t="n">
-        <v>0.035609</v>
+        <v>0.06</v>
       </c>
       <c r="M273" s="5" t="n">
-        <v>0.038963</v>
+        <v>0.06</v>
       </c>
       <c r="N273" s="5" t="n">
-        <v>0.039768</v>
+        <v>0.06</v>
       </c>
       <c r="O273" s="5" t="n">
-        <v>0.039685</v>
+        <v>0.06</v>
       </c>
       <c r="P273" s="5" t="n">
-        <v>0.115036</v>
+        <v>0.06</v>
       </c>
       <c r="Q273" s="5" t="n">
-        <v>0.132166</v>
+        <v>0.06</v>
       </c>
       <c r="R273" s="5" t="n">
-        <v>0.111129</v>
+        <v>0.05</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -33525,24 +33549,24 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Exploration and evaluation, net of recoveries 8 &amp; 9</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>Consulting 9</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F274" s="5" t="n">
+        <v>0.216905</v>
+      </c>
+      <c r="G274" s="5" t="n">
+        <v>0.172611</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -33554,42 +33578,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J274" s="5" t="n">
+        <v>0.07275</v>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>0.028543</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>0.035609</v>
+      </c>
+      <c r="M274" s="5" t="n">
+        <v>0.038963</v>
+      </c>
+      <c r="N274" s="5" t="n">
+        <v>0.039768</v>
       </c>
       <c r="O274" s="5" t="n">
-        <v>0.104479</v>
+        <v>0.039685</v>
       </c>
       <c r="P274" s="5" t="n">
-        <v>0.6546650000000001</v>
+        <v>0.115036</v>
       </c>
       <c r="Q274" s="5" t="n">
-        <v>0.608056</v>
+        <v>0.132166</v>
       </c>
       <c r="R274" s="5" t="n">
-        <v>0.329794</v>
+        <v>0.111129</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -33615,24 +33629,24 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Investor relations 9</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation, net of recoveries 8 &amp; 9</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F275" s="5" t="n">
-        <v>0.16228</v>
-      </c>
-      <c r="G275" s="5" t="n">
-        <v>0.143826</v>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -33644,32 +33658,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J275" s="5" t="n">
-        <v>0.002211</v>
-      </c>
-      <c r="K275" s="5" t="n">
-        <v>0.07215199999999999</v>
-      </c>
-      <c r="L275" s="5" t="n">
-        <v>0.187003</v>
-      </c>
-      <c r="M275" s="5" t="n">
-        <v>0.234035</v>
-      </c>
-      <c r="N275" s="5" t="n">
-        <v>0.186534</v>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O275" s="5" t="n">
-        <v>0.105829</v>
+        <v>0.104479</v>
       </c>
       <c r="P275" s="5" t="n">
-        <v>0.130105</v>
+        <v>0.6546650000000001</v>
       </c>
       <c r="Q275" s="5" t="n">
-        <v>0.09321400000000001</v>
+        <v>0.608056</v>
       </c>
       <c r="R275" s="5" t="n">
-        <v>0.0835</v>
+        <v>0.329794</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -33695,7 +33719,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Office and general 9</t>
+          <t>Investor relations 9</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33709,10 +33733,10 @@
         </is>
       </c>
       <c r="F276" s="5" t="n">
-        <v>0.132144</v>
+        <v>0.16228</v>
       </c>
       <c r="G276" s="5" t="n">
-        <v>0.095052</v>
+        <v>0.143826</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -33725,31 +33749,31 @@
         </is>
       </c>
       <c r="J276" s="5" t="n">
-        <v>0.043618</v>
+        <v>0.002211</v>
       </c>
       <c r="K276" s="5" t="n">
-        <v>0.053076</v>
+        <v>0.07215199999999999</v>
       </c>
       <c r="L276" s="5" t="n">
-        <v>0.06338199999999999</v>
+        <v>0.187003</v>
       </c>
       <c r="M276" s="5" t="n">
-        <v>0.057375</v>
+        <v>0.234035</v>
       </c>
       <c r="N276" s="5" t="n">
-        <v>0.056118</v>
+        <v>0.186534</v>
       </c>
       <c r="O276" s="5" t="n">
-        <v>0.055619</v>
+        <v>0.105829</v>
       </c>
       <c r="P276" s="5" t="n">
-        <v>0.05362</v>
+        <v>0.130105</v>
       </c>
       <c r="Q276" s="5" t="n">
-        <v>0.05462</v>
+        <v>0.09321400000000001</v>
       </c>
       <c r="R276" s="5" t="n">
-        <v>0.058611</v>
+        <v>0.0835</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -33775,12 +33799,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Professional fees 9</t>
+          <t>Office and general 9</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -33789,10 +33813,10 @@
         </is>
       </c>
       <c r="F277" s="5" t="n">
-        <v>0.195436</v>
+        <v>0.132144</v>
       </c>
       <c r="G277" s="5" t="n">
-        <v>0.150487</v>
+        <v>0.095052</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -33805,31 +33829,31 @@
         </is>
       </c>
       <c r="J277" s="5" t="n">
-        <v>0.024592</v>
+        <v>0.043618</v>
       </c>
       <c r="K277" s="5" t="n">
-        <v>0.0412</v>
+        <v>0.053076</v>
       </c>
       <c r="L277" s="5" t="n">
-        <v>0.149552</v>
+        <v>0.06338199999999999</v>
       </c>
       <c r="M277" s="5" t="n">
-        <v>0.09747400000000001</v>
+        <v>0.057375</v>
       </c>
       <c r="N277" s="5" t="n">
-        <v>0.106432</v>
+        <v>0.056118</v>
       </c>
       <c r="O277" s="5" t="n">
-        <v>0.090568</v>
+        <v>0.055619</v>
       </c>
       <c r="P277" s="5" t="n">
-        <v>0.084282</v>
+        <v>0.05362</v>
       </c>
       <c r="Q277" s="5" t="n">
-        <v>0.064183</v>
+        <v>0.05462</v>
       </c>
       <c r="R277" s="5" t="n">
-        <v>0.072994</v>
+        <v>0.058611</v>
       </c>
       <c r="S277" t="inlineStr">
         <is>
@@ -33855,53 +33879,61 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Regulatory fees and taxes</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>Professional fees 9</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F278" s="5" t="n">
-        <v>0.023935</v>
+        <v>0.195436</v>
       </c>
       <c r="G278" s="5" t="n">
-        <v>0.018315</v>
-      </c>
-      <c r="H278" s="5" t="n">
-        <v>0.013302</v>
-      </c>
-      <c r="I278" s="5" t="n">
-        <v>0.012764</v>
+        <v>0.150487</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J278" s="5" t="n">
-        <v>0.009291000000000001</v>
+        <v>0.024592</v>
       </c>
       <c r="K278" s="5" t="n">
-        <v>0.010942</v>
+        <v>0.0412</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>0.031389</v>
+        <v>0.149552</v>
       </c>
       <c r="M278" s="5" t="n">
-        <v>0.0258</v>
+        <v>0.09747400000000001</v>
       </c>
       <c r="N278" s="5" t="n">
-        <v>0.02586</v>
+        <v>0.106432</v>
       </c>
       <c r="O278" s="5" t="n">
-        <v>0.028</v>
+        <v>0.090568</v>
       </c>
       <c r="P278" s="5" t="n">
-        <v>0.032243</v>
+        <v>0.084282</v>
       </c>
       <c r="Q278" s="5" t="n">
-        <v>0.029641</v>
+        <v>0.064183</v>
       </c>
       <c r="R278" s="5" t="n">
-        <v>0.034044</v>
+        <v>0.072994</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -33927,7 +33959,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Share-based payments 10</t>
+          <t>Regulatory fees and taxes</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -33936,64 +33968,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F279" s="5" t="n">
+        <v>0.023935</v>
+      </c>
+      <c r="G279" s="5" t="n">
+        <v>0.018315</v>
+      </c>
+      <c r="H279" s="5" t="n">
+        <v>0.013302</v>
+      </c>
+      <c r="I279" s="5" t="n">
+        <v>0.012764</v>
+      </c>
+      <c r="J279" s="5" t="n">
+        <v>0.009291000000000001</v>
+      </c>
+      <c r="K279" s="5" t="n">
+        <v>0.010942</v>
+      </c>
+      <c r="L279" s="5" t="n">
+        <v>0.031389</v>
+      </c>
+      <c r="M279" s="5" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="N279" s="5" t="n">
+        <v>0.02586</v>
       </c>
       <c r="O279" s="5" t="n">
-        <v>0.003279</v>
+        <v>0.028</v>
       </c>
       <c r="P279" s="5" t="n">
-        <v>0.298171</v>
+        <v>0.032243</v>
       </c>
       <c r="Q279" s="5" t="n">
-        <v>0.261325</v>
-      </c>
-      <c r="R279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.029641</v>
+      </c>
+      <c r="R279" s="5" t="n">
+        <v>0.034044</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -34019,14 +34031,10 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Shareholders' communications</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based payments 10</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -34042,38 +34050,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H280" s="5" t="n">
-        <v>0.008540000000000001</v>
-      </c>
-      <c r="I280" s="5" t="n">
-        <v>0.016212</v>
-      </c>
-      <c r="J280" s="5" t="n">
-        <v>0.012627</v>
-      </c>
-      <c r="K280" s="5" t="n">
-        <v>0.003304</v>
-      </c>
-      <c r="L280" s="5" t="n">
-        <v>0.006019</v>
-      </c>
-      <c r="M280" s="5" t="n">
-        <v>0.010882</v>
-      </c>
-      <c r="N280" s="5" t="n">
-        <v>0.009050000000000001</v>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O280" s="5" t="n">
-        <v>0.007622</v>
+        <v>0.003279</v>
       </c>
       <c r="P280" s="5" t="n">
-        <v>0.01557</v>
+        <v>0.298171</v>
       </c>
       <c r="Q280" s="5" t="n">
-        <v>0.010856</v>
-      </c>
-      <c r="R280" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.261325</v>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -34099,12 +34123,12 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
+          <t>Shareholders' communications</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -34112,44 +34136,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F281" s="5" t="n">
-        <v>0.059128</v>
-      </c>
-      <c r="G281" s="5" t="n">
-        <v>0.02917</v>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H281" s="5" t="n">
-        <v>0.017919</v>
+        <v>0.008540000000000001</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>0.019068</v>
+        <v>0.016212</v>
       </c>
       <c r="J281" s="5" t="n">
-        <v>0.005991</v>
+        <v>0.012627</v>
       </c>
       <c r="K281" s="5" t="n">
-        <v>0.01255</v>
+        <v>0.003304</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>0.014526</v>
+        <v>0.006019</v>
       </c>
       <c r="M281" s="5" t="n">
-        <v>0.009535999999999999</v>
+        <v>0.010882</v>
       </c>
       <c r="N281" s="5" t="n">
-        <v>0.013001</v>
+        <v>0.009050000000000001</v>
       </c>
       <c r="O281" s="5" t="n">
-        <v>0.013671</v>
+        <v>0.007622</v>
       </c>
       <c r="P281" s="5" t="n">
-        <v>0.015245</v>
+        <v>0.01557</v>
       </c>
       <c r="Q281" s="5" t="n">
-        <v>0.014369</v>
+        <v>0.010856</v>
       </c>
       <c r="R281" s="5" t="n">
-        <v>0.014828</v>
+        <v>0.0094</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
@@ -34175,12 +34203,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Operating Expenses total</t>
+          <t>Transfer agent</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -34189,43 +34217,43 @@
         </is>
       </c>
       <c r="F282" s="5" t="n">
-        <v>2.934087</v>
+        <v>0.059128</v>
       </c>
       <c r="G282" s="5" t="n">
-        <v>1.525395</v>
+        <v>0.02917</v>
       </c>
       <c r="H282" s="5" t="n">
-        <v>0.699786</v>
+        <v>0.017919</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>0.251002</v>
+        <v>0.019068</v>
       </c>
       <c r="J282" s="5" t="n">
-        <v>0.043497</v>
+        <v>0.005991</v>
       </c>
       <c r="K282" s="5" t="n">
-        <v>0.5945859999999999</v>
+        <v>0.01255</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>1.037197</v>
+        <v>0.014526</v>
       </c>
       <c r="M282" s="5" t="n">
-        <v>1.043373</v>
+        <v>0.009535999999999999</v>
       </c>
       <c r="N282" s="5" t="n">
-        <v>0.806304</v>
+        <v>0.013001</v>
       </c>
       <c r="O282" s="5" t="n">
-        <v>0.508752</v>
+        <v>0.013671</v>
       </c>
       <c r="P282" s="5" t="n">
-        <v>1.458937</v>
+        <v>0.015245</v>
       </c>
       <c r="Q282" s="5" t="n">
-        <v>1.32843</v>
+        <v>0.014369</v>
       </c>
       <c r="R282" s="5" t="n">
-        <v>0.7643</v>
+        <v>0.014828</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
@@ -34251,12 +34279,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
+          <t>Operating Expenses total</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -34265,51 +34293,43 @@
         </is>
       </c>
       <c r="F283" s="5" t="n">
-        <v>0.020516</v>
+        <v>2.934087</v>
       </c>
       <c r="G283" s="5" t="n">
-        <v>-0.004138</v>
+        <v>1.525395</v>
       </c>
       <c r="H283" s="5" t="n">
-        <v>0.005378</v>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.699786</v>
+      </c>
+      <c r="I283" s="5" t="n">
+        <v>0.251002</v>
       </c>
       <c r="J283" s="5" t="n">
-        <v>0.049059</v>
+        <v>0.043497</v>
       </c>
       <c r="K283" s="5" t="n">
-        <v>-0.008937</v>
-      </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5945859999999999</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>1.037197</v>
+      </c>
+      <c r="M283" s="5" t="n">
+        <v>1.043373</v>
+      </c>
+      <c r="N283" s="5" t="n">
+        <v>0.806304</v>
       </c>
       <c r="O283" s="5" t="n">
-        <v>0.009523999999999999</v>
+        <v>0.508752</v>
       </c>
       <c r="P283" s="5" t="n">
-        <v>-0.0226</v>
+        <v>1.458937</v>
       </c>
       <c r="Q283" s="5" t="n">
-        <v>0.001667</v>
+        <v>1.32843</v>
       </c>
       <c r="R283" s="5" t="n">
-        <v>-0.004643</v>
+        <v>0.7643</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
@@ -34335,67 +34355,65 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties 8</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
+          <t>Foreign exchange (gain) loss</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F284" s="5" t="n">
+        <v>0.020516</v>
+      </c>
+      <c r="G284" s="5" t="n">
+        <v>-0.004138</v>
+      </c>
+      <c r="H284" s="5" t="n">
+        <v>0.005378</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J284" s="5" t="n">
+        <v>0.049059</v>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>-0.008937</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M284" s="5" t="n">
-        <v>0.289817</v>
-      </c>
-      <c r="N284" s="5" t="n">
-        <v>0.205563</v>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O284" s="5" t="n">
-        <v>0.086003</v>
+        <v>0.009523999999999999</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.173078</v>
+        <v>-0.0226</v>
       </c>
       <c r="Q284" s="5" t="n">
-        <v>0.098159</v>
+        <v>0.001667</v>
       </c>
       <c r="R284" s="5" t="n">
-        <v>0.12219</v>
+        <v>-0.004643</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
@@ -34421,7 +34439,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Interest on overdue debt</t>
+          <t>Impairment of mineral properties 8</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -34465,33 +34483,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M285" s="5" t="n">
+        <v>0.289817</v>
+      </c>
+      <c r="N285" s="5" t="n">
+        <v>0.205563</v>
+      </c>
+      <c r="O285" s="5" t="n">
+        <v>0.086003</v>
+      </c>
+      <c r="P285" s="5" t="n">
+        <v>0.173078</v>
+      </c>
+      <c r="Q285" s="5" t="n">
+        <v>0.098159</v>
       </c>
       <c r="R285" s="5" t="n">
-        <v>0.020446</v>
+        <v>0.12219</v>
       </c>
       <c r="S285" t="inlineStr">
         <is>
@@ -34517,14 +34525,10 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Interest on overdue debt</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -34575,17 +34579,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O286" s="5" t="n">
-        <v>-0.611495</v>
-      </c>
-      <c r="P286" s="5" t="n">
-        <v>-1.593073</v>
-      </c>
-      <c r="Q286" s="5" t="n">
-        <v>-1.428256</v>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R286" s="5" t="n">
-        <v>-0.902293</v>
+        <v>0.020446</v>
       </c>
       <c r="S286" t="inlineStr">
         <is>
@@ -34611,12 +34621,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -34670,16 +34680,16 @@
         </is>
       </c>
       <c r="O287" s="5" t="n">
-        <v>1e-08</v>
+        <v>-0.611495</v>
       </c>
       <c r="P287" s="5" t="n">
-        <v>2e-08</v>
+        <v>-1.593073</v>
       </c>
       <c r="Q287" s="5" t="n">
-        <v>1e-08</v>
+        <v>-1.428256</v>
       </c>
       <c r="R287" s="5" t="n">
-        <v>1e-08</v>
+        <v>-0.902293</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
@@ -34705,12 +34715,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Loss per share - basic and diluted $</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -34764,16 +34774,16 @@
         </is>
       </c>
       <c r="O288" s="5" t="n">
-        <v>69.72759600000001</v>
+        <v>1e-08</v>
       </c>
       <c r="P288" s="5" t="n">
-        <v>88.32775100000001</v>
+        <v>2e-08</v>
       </c>
       <c r="Q288" s="5" t="n">
-        <v>105.723622</v>
+        <v>1e-08</v>
       </c>
       <c r="R288" s="5" t="n">
-        <v>131.27768</v>
+        <v>1e-08</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
@@ -34799,10 +34809,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Operator fee income</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -34818,42 +34832,52 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H289" s="5" t="n">
-        <v>-0.047357</v>
-      </c>
-      <c r="I289" s="5" t="n">
-        <v>-0.003142</v>
-      </c>
-      <c r="J289" s="5" t="n">
-        <v>-0.000593</v>
-      </c>
-      <c r="K289" s="5" t="n">
-        <v>-0.012506</v>
-      </c>
-      <c r="L289" s="5" t="n">
-        <v>-0.010037</v>
-      </c>
-      <c r="M289" s="5" t="n">
-        <v>-0.001371</v>
-      </c>
-      <c r="N289" s="5" t="n">
-        <v>-0.00122</v>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O289" s="5" t="n">
-        <v>-0.002911</v>
+        <v>69.72759600000001</v>
       </c>
       <c r="P289" s="5" t="n">
-        <v>-0.016342</v>
-      </c>
-      <c r="Q289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>88.32775100000001</v>
+      </c>
+      <c r="Q289" s="5" t="n">
+        <v>105.723622</v>
+      </c>
+      <c r="R289" s="5" t="n">
+        <v>131.27768</v>
       </c>
       <c r="S289" t="inlineStr">
         <is>
@@ -34879,14 +34903,10 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Operator fee income</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -34902,38 +34922,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H290" s="5" t="n">
+        <v>-0.047357</v>
+      </c>
+      <c r="I290" s="5" t="n">
+        <v>-0.003142</v>
       </c>
       <c r="J290" s="5" t="n">
-        <v>0.0365</v>
+        <v>-0.000593</v>
       </c>
       <c r="K290" s="5" t="n">
-        <v>-0.012766</v>
+        <v>-0.012506</v>
       </c>
       <c r="L290" s="5" t="n">
-        <v>0.008992999999999999</v>
+        <v>-0.010037</v>
       </c>
       <c r="M290" s="5" t="n">
-        <v>0.004735</v>
+        <v>-0.001371</v>
       </c>
       <c r="N290" s="5" t="n">
-        <v>0.003779</v>
+        <v>-0.00122</v>
       </c>
       <c r="O290" s="5" t="n">
-        <v>0.010127</v>
-      </c>
-      <c r="P290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.002911</v>
+      </c>
+      <c r="P290" s="5" t="n">
+        <v>-0.016342</v>
       </c>
       <c r="Q290" t="inlineStr">
         <is>
@@ -34969,10 +34983,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Exploration and evaluation, net of recoveries 8(d) &amp; 9</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr"/>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -34998,31 +35016,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J291" s="5" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="K291" s="5" t="n">
+        <v>-0.012766</v>
+      </c>
+      <c r="L291" s="5" t="n">
+        <v>0.008992999999999999</v>
       </c>
       <c r="M291" s="5" t="n">
-        <v>0.397711</v>
+        <v>0.004735</v>
       </c>
       <c r="N291" s="5" t="n">
-        <v>0.264792</v>
-      </c>
-      <c r="O291" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003779</v>
+      </c>
+      <c r="O291" s="5" t="n">
+        <v>0.010127</v>
       </c>
       <c r="P291" t="inlineStr">
         <is>
@@ -35063,7 +35073,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Share-based payments 10(e)</t>
+          <t>Exploration and evaluation, net of recoveries 8(d) &amp; 9</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -35102,14 +35112,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L292" s="5" t="n">
-        <v>0.403414</v>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M292" s="5" t="n">
-        <v>0.106772</v>
+        <v>0.397711</v>
       </c>
       <c r="N292" s="5" t="n">
-        <v>0.042488</v>
+        <v>0.264792</v>
       </c>
       <c r="O292" t="inlineStr">
         <is>
@@ -35155,45 +35167,53 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Travel and promotion</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Share-based payments 10(e)</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F293" s="5" t="n">
-        <v>0.08303000000000001</v>
-      </c>
-      <c r="G293" s="5" t="n">
-        <v>0.025124</v>
-      </c>
-      <c r="H293" s="5" t="n">
-        <v>0.013807</v>
-      </c>
-      <c r="I293" s="5" t="n">
-        <v>0.01833</v>
-      </c>
-      <c r="J293" s="5" t="n">
-        <v>0.002533</v>
-      </c>
-      <c r="K293" s="5" t="n">
-        <v>0.010118</v>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L293" s="5" t="n">
-        <v>0.002156</v>
+        <v>0.403414</v>
       </c>
       <c r="M293" s="5" t="n">
-        <v>0.004825</v>
+        <v>0.106772</v>
       </c>
       <c r="N293" s="5" t="n">
-        <v>0.002261</v>
+        <v>0.042488</v>
       </c>
       <c r="O293" t="inlineStr">
         <is>
@@ -35239,12 +35259,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Travel and promotion</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -35252,40 +35272,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F294" s="5" t="n">
+        <v>0.08303000000000001</v>
+      </c>
+      <c r="G294" s="5" t="n">
+        <v>0.025124</v>
       </c>
       <c r="H294" s="5" t="n">
-        <v>0.005378</v>
+        <v>0.013807</v>
       </c>
       <c r="I294" s="5" t="n">
-        <v>0.006575</v>
+        <v>0.01833</v>
       </c>
       <c r="J294" s="5" t="n">
-        <v>0.049059</v>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002533</v>
+      </c>
+      <c r="K294" s="5" t="n">
+        <v>0.010118</v>
+      </c>
+      <c r="L294" s="5" t="n">
+        <v>0.002156</v>
       </c>
       <c r="M294" s="5" t="n">
-        <v>0.014044</v>
+        <v>0.004825</v>
       </c>
       <c r="N294" s="5" t="n">
-        <v>0.001828</v>
+        <v>0.002261</v>
       </c>
       <c r="O294" t="inlineStr">
         <is>
@@ -35331,10 +35343,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Realized gain on sale of marketable securities</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -35350,20 +35366,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H295" s="5" t="n">
+        <v>0.005378</v>
+      </c>
+      <c r="I295" s="5" t="n">
+        <v>0.006575</v>
+      </c>
+      <c r="J295" s="5" t="n">
+        <v>0.049059</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -35376,12 +35386,10 @@
         </is>
       </c>
       <c r="M295" s="5" t="n">
-        <v>-0.006396</v>
-      </c>
-      <c r="N295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014044</v>
+      </c>
+      <c r="N295" s="5" t="n">
+        <v>0.001828</v>
       </c>
       <c r="O295" t="inlineStr">
         <is>
@@ -35427,45 +35435,57 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Net Loss for the Year</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Realized gain on sale of marketable securities</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F296" s="5" t="n">
-        <v>-3.352988</v>
-      </c>
-      <c r="G296" s="5" t="n">
-        <v>-3.244691</v>
-      </c>
-      <c r="H296" s="5" t="n">
-        <v>-8.837339</v>
-      </c>
-      <c r="I296" s="5" t="n">
-        <v>-0.671818</v>
-      </c>
-      <c r="J296" s="5" t="n">
-        <v>-0.154075</v>
-      </c>
-      <c r="K296" s="5" t="n">
-        <v>-1.693076</v>
-      </c>
-      <c r="L296" s="5" t="n">
-        <v>-1.182866</v>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M296" s="5" t="n">
-        <v>-1.344202</v>
-      </c>
-      <c r="N296" s="5" t="n">
-        <v>-1.016254</v>
+        <v>-0.006396</v>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O296" t="inlineStr">
         <is>
@@ -35506,62 +35526,50 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Reclassification adjustment for realized gain on sale of</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Reclassification adjustment for realized gain on sale of marketable securities included in net loss</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>Net Loss for the Year</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F297" s="5" t="n">
+        <v>-3.352988</v>
+      </c>
+      <c r="G297" s="5" t="n">
+        <v>-3.244691</v>
+      </c>
+      <c r="H297" s="5" t="n">
+        <v>-8.837339</v>
+      </c>
+      <c r="I297" s="5" t="n">
+        <v>-0.671818</v>
+      </c>
+      <c r="J297" s="5" t="n">
+        <v>-0.154075</v>
+      </c>
+      <c r="K297" s="5" t="n">
+        <v>-1.693076</v>
+      </c>
+      <c r="L297" s="5" t="n">
+        <v>-1.182866</v>
       </c>
       <c r="M297" s="5" t="n">
-        <v>0.006396</v>
-      </c>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.344202</v>
+      </c>
+      <c r="N297" s="5" t="n">
+        <v>-1.016254</v>
       </c>
       <c r="O297" t="inlineStr">
         <is>
@@ -35607,7 +35615,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Unrealized loss on fair value of marketable securities</t>
+          <t>Reclassification adjustment for realized gain on sale of marketable securities included in net loss</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -35652,7 +35660,7 @@
         </is>
       </c>
       <c r="M298" s="5" t="n">
-        <v>0.001461</v>
+        <v>0.006396</v>
       </c>
       <c r="N298" t="inlineStr">
         <is>
@@ -35703,14 +35711,10 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Unrealized loss on fair value of marketable securities</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -35736,11 +35740,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J299" s="5" t="n">
-        <v>-0.136305</v>
-      </c>
-      <c r="K299" s="5" t="n">
-        <v>-1.678346</v>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -35748,10 +35756,12 @@
         </is>
       </c>
       <c r="M299" s="5" t="n">
-        <v>-1.352059</v>
-      </c>
-      <c r="N299" s="5" t="n">
-        <v>-1.016254</v>
+        <v>0.001461</v>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -35797,12 +35807,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -35831,10 +35841,10 @@
         </is>
       </c>
       <c r="J300" s="5" t="n">
-        <v>1e-08</v>
+        <v>-0.136305</v>
       </c>
       <c r="K300" s="5" t="n">
-        <v>8e-08</v>
+        <v>-1.678346</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -35842,10 +35852,10 @@
         </is>
       </c>
       <c r="M300" s="5" t="n">
-        <v>3e-08</v>
+        <v>-1.352059</v>
       </c>
       <c r="N300" s="5" t="n">
-        <v>2e-08</v>
+        <v>-1.016254</v>
       </c>
       <c r="O300" t="inlineStr">
         <is>
@@ -35891,12 +35901,12 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Loss per share - basic and diluted $</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -35925,10 +35935,10 @@
         </is>
       </c>
       <c r="J301" s="5" t="n">
-        <v>11.97021</v>
+        <v>1e-08</v>
       </c>
       <c r="K301" s="5" t="n">
-        <v>21.590573</v>
+        <v>8e-08</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -35936,10 +35946,10 @@
         </is>
       </c>
       <c r="M301" s="5" t="n">
-        <v>45.33196</v>
+        <v>3e-08</v>
       </c>
       <c r="N301" s="5" t="n">
-        <v>57.210237</v>
+        <v>2e-08</v>
       </c>
       <c r="O301" t="inlineStr">
         <is>
@@ -35980,15 +35990,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Reclassification adjustment for realized gain on sale of</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Exploration and evaluation, net of recoveries 7(d) &amp; 9</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -36014,26 +36028,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L302" s="5" t="n">
-        <v>0.084147</v>
+      <c r="J302" s="5" t="n">
+        <v>11.97021</v>
+      </c>
+      <c r="K302" s="5" t="n">
+        <v>21.590573</v>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.397711</v>
-      </c>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>45.33196</v>
+      </c>
+      <c r="N302" s="5" t="n">
+        <v>57.210237</v>
       </c>
       <c r="O302" t="inlineStr">
         <is>
@@ -36079,14 +36089,10 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation, net of recoveries 7(d) &amp; 9</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -36123,10 +36129,10 @@
         </is>
       </c>
       <c r="L303" s="5" t="n">
-        <v>-0.014265</v>
+        <v>0.084147</v>
       </c>
       <c r="M303" s="5" t="n">
-        <v>0.014044</v>
+        <v>0.397711</v>
       </c>
       <c r="N303" t="inlineStr">
         <is>
@@ -36177,10 +36183,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Impairment of marketable securities 6</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -36206,19 +36216,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J304" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K304" s="5" t="n">
-        <v>0.050676</v>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L304" s="5" t="n">
-        <v>0.009998999999999999</v>
-      </c>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.014265</v>
+      </c>
+      <c r="M304" s="5" t="n">
+        <v>0.014044</v>
       </c>
       <c r="N304" t="inlineStr">
         <is>
@@ -36269,7 +36281,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties 7</t>
+          <t>Impairment of marketable securities 6</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -36278,29 +36290,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F305" s="5" t="n">
-        <v>0.406024</v>
-      </c>
-      <c r="G305" s="5" t="n">
-        <v>1.725961</v>
-      </c>
-      <c r="H305" s="5" t="n">
-        <v>8.138277</v>
-      </c>
-      <c r="I305" s="5" t="n">
-        <v>0.396105</v>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J305" s="5" t="n">
-        <v>0.08268300000000001</v>
+        <v>0.02</v>
       </c>
       <c r="K305" s="5" t="n">
-        <v>0.245872</v>
+        <v>0.050676</v>
       </c>
       <c r="L305" s="5" t="n">
-        <v>0.143314</v>
-      </c>
-      <c r="M305" s="5" t="n">
-        <v>0.289817</v>
+        <v>0.009998999999999999</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
@@ -36351,7 +36373,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Realized (gain) loss on sale of marketable securities 6</t>
+          <t>Impairment of mineral properties 7</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -36360,37 +36382,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F306" s="5" t="n">
+        <v>0.406024</v>
+      </c>
+      <c r="G306" s="5" t="n">
+        <v>1.725961</v>
+      </c>
+      <c r="H306" s="5" t="n">
+        <v>8.138277</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>0.017244</v>
+        <v>0.396105</v>
       </c>
       <c r="J306" s="5" t="n">
-        <v>-0.003394</v>
-      </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.08268300000000001</v>
+      </c>
+      <c r="K306" s="5" t="n">
+        <v>0.245872</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>0.007665</v>
+        <v>0.143314</v>
       </c>
       <c r="M306" s="5" t="n">
-        <v>-0.006396</v>
+        <v>0.289817</v>
       </c>
       <c r="N306" t="inlineStr">
         <is>
@@ -36436,12 +36450,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Other Comprehensive Loss</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Reclassification adjustment for realized gain (loss) on sale of marketable securities included in net loss 6</t>
+          <t>Realized (gain) loss on sale of marketable securities 6</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -36465,15 +36479,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I307" s="5" t="n">
+        <v>0.017244</v>
+      </c>
+      <c r="J307" s="5" t="n">
+        <v>-0.003394</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
@@ -36481,10 +36491,10 @@
         </is>
       </c>
       <c r="L307" s="5" t="n">
-        <v>-0.007665</v>
+        <v>0.007665</v>
       </c>
       <c r="M307" s="5" t="n">
-        <v>0.006396</v>
+        <v>-0.006396</v>
       </c>
       <c r="N307" t="inlineStr">
         <is>
@@ -36535,7 +36545,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Unrealized loss on fair value of marketable securities 6</t>
+          <t>Reclassification adjustment for realized gain (loss) on sale of marketable securities included in net loss 6</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -36575,10 +36585,10 @@
         </is>
       </c>
       <c r="L308" s="5" t="n">
-        <v>0.034808</v>
+        <v>-0.007665</v>
       </c>
       <c r="M308" s="5" t="n">
-        <v>0.001461</v>
+        <v>0.006396</v>
       </c>
       <c r="N308" t="inlineStr">
         <is>
@@ -36629,24 +36639,24 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Unrealized loss on fair value of marketable securities 6</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F309" s="5" t="n">
-        <v>-3.355488</v>
-      </c>
-      <c r="G309" s="5" t="n">
-        <v>-3.247191</v>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
@@ -36669,10 +36679,10 @@
         </is>
       </c>
       <c r="L309" s="5" t="n">
-        <v>-1.210009</v>
+        <v>0.034808</v>
       </c>
       <c r="M309" s="5" t="n">
-        <v>-1.352059</v>
+        <v>0.001461</v>
       </c>
       <c r="N309" t="inlineStr">
         <is>
@@ -36723,12 +36733,12 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -36736,15 +36746,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F310" s="5" t="n">
+        <v>-3.355488</v>
+      </c>
+      <c r="G310" s="5" t="n">
+        <v>-3.247191</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
@@ -36767,10 +36773,10 @@
         </is>
       </c>
       <c r="L310" s="5" t="n">
-        <v>3e-08</v>
+        <v>-1.210009</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>3e-08</v>
+        <v>-1.352059</v>
       </c>
       <c r="N310" t="inlineStr">
         <is>
@@ -36821,12 +36827,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Loss per share - basic and diluted $</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -36834,11 +36840,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F311" s="5" t="n">
-        <v>59.731207</v>
-      </c>
-      <c r="G311" s="5" t="n">
-        <v>109.034693</v>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
@@ -36861,10 +36871,10 @@
         </is>
       </c>
       <c r="L311" s="5" t="n">
-        <v>36.58422</v>
+        <v>3e-08</v>
       </c>
       <c r="M311" s="5" t="n">
-        <v>45.33196</v>
+        <v>3e-08</v>
       </c>
       <c r="N311" t="inlineStr">
         <is>
@@ -36910,29 +36920,29 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Comprehensive Loss</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Exploration and evaluation, net of recoveries 7(f) &amp; 9</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F312" s="5" t="n">
+        <v>59.731207</v>
+      </c>
+      <c r="G312" s="5" t="n">
+        <v>109.034693</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -36944,19 +36954,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J312" s="5" t="n">
-        <v>-0.268845</v>
-      </c>
-      <c r="K312" s="5" t="n">
-        <v>0.057648</v>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L312" s="5" t="n">
-        <v>0.084147</v>
-      </c>
-      <c r="M312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>36.58422</v>
+      </c>
+      <c r="M312" s="5" t="n">
+        <v>45.33196</v>
       </c>
       <c r="N312" t="inlineStr">
         <is>
@@ -37007,7 +37019,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Share-based payments 11(f)</t>
+          <t>Exploration and evaluation, net of recoveries 7(f) &amp; 9</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -37037,13 +37049,13 @@
         </is>
       </c>
       <c r="J313" s="5" t="n">
-        <v>0.051735</v>
+        <v>-0.268845</v>
       </c>
       <c r="K313" s="5" t="n">
-        <v>0.245053</v>
+        <v>0.057648</v>
       </c>
       <c r="L313" s="5" t="n">
-        <v>0.403414</v>
+        <v>0.084147</v>
       </c>
       <c r="M313" t="inlineStr">
         <is>
@@ -37099,14 +37111,10 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share-based payments 11(f)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -37132,16 +37140,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J314" s="5" t="n">
+        <v>0.051735</v>
       </c>
       <c r="K314" s="5" t="n">
-        <v>-0.008937</v>
+        <v>0.245053</v>
       </c>
       <c r="L314" s="5" t="n">
-        <v>-0.014265</v>
+        <v>0.403414</v>
       </c>
       <c r="M314" t="inlineStr">
         <is>
@@ -37197,10 +37203,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Interest accretion 10</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -37216,22 +37226,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H315" s="5" t="n">
-        <v>0.041388</v>
-      </c>
-      <c r="I315" s="5" t="n">
-        <v>0.014095</v>
-      </c>
-      <c r="J315" s="5" t="n">
-        <v>0.013397</v>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K315" s="5" t="n">
-        <v>0.010267</v>
-      </c>
-      <c r="L315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008937</v>
+      </c>
+      <c r="L315" s="5" t="n">
+        <v>-0.014265</v>
       </c>
       <c r="M315" t="inlineStr">
         <is>
@@ -37287,7 +37301,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt 11(c)</t>
+          <t>Interest accretion 10</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -37306,23 +37320,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H316" s="5" t="n">
+        <v>0.041388</v>
+      </c>
+      <c r="I316" s="5" t="n">
+        <v>0.014095</v>
+      </c>
+      <c r="J316" s="5" t="n">
+        <v>0.013397</v>
       </c>
       <c r="K316" s="5" t="n">
-        <v>0.842776</v>
+        <v>0.010267</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
@@ -37383,7 +37391,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Realized loss (gain) on sale of marketable securities 6</t>
+          <t>Loss on settlement of debt 11(c)</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -37418,10 +37426,12 @@
         </is>
       </c>
       <c r="K317" s="5" t="n">
-        <v>-0.016892</v>
-      </c>
-      <c r="L317" s="5" t="n">
-        <v>0.007665</v>
+        <v>0.842776</v>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
@@ -37472,12 +37482,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Reclassification adjustment for realized (loss) gain on sale</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Reclassification adjustment for realized (loss) gain on sale of marketable securities included in net loss 6</t>
+          <t>Realized loss (gain) on sale of marketable securities 6</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -37512,10 +37522,10 @@
         </is>
       </c>
       <c r="K318" s="5" t="n">
-        <v>0.016892</v>
+        <v>-0.016892</v>
       </c>
       <c r="L318" s="5" t="n">
-        <v>-0.007665</v>
+        <v>0.007665</v>
       </c>
       <c r="M318" t="inlineStr">
         <is>
@@ -37571,7 +37581,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Unrealized loss (gain) on fair value of marketable securities 6</t>
+          <t>Reclassification adjustment for realized (loss) gain on sale of marketable securities included in net loss 6</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -37606,10 +37616,10 @@
         </is>
       </c>
       <c r="K319" s="5" t="n">
-        <v>-0.031622</v>
+        <v>0.016892</v>
       </c>
       <c r="L319" s="5" t="n">
-        <v>0.034808</v>
+        <v>-0.007665</v>
       </c>
       <c r="M319" t="inlineStr">
         <is>
@@ -37665,14 +37675,10 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Unrealized loss (gain) on fair value of marketable securities 6</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -37704,10 +37710,10 @@
         </is>
       </c>
       <c r="K320" s="5" t="n">
-        <v>-1.678346</v>
+        <v>-0.031622</v>
       </c>
       <c r="L320" s="5" t="n">
-        <v>-1.210009</v>
+        <v>0.034808</v>
       </c>
       <c r="M320" t="inlineStr">
         <is>
@@ -37763,12 +37769,12 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -37802,10 +37808,10 @@
         </is>
       </c>
       <c r="K321" s="5" t="n">
-        <v>8e-08</v>
+        <v>-1.678346</v>
       </c>
       <c r="L321" s="5" t="n">
-        <v>3e-08</v>
+        <v>-1.210009</v>
       </c>
       <c r="M321" t="inlineStr">
         <is>
@@ -37861,12 +37867,12 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Loss per share - basic and diluted $</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -37900,10 +37906,10 @@
         </is>
       </c>
       <c r="K322" s="5" t="n">
-        <v>21.590573</v>
+        <v>8e-08</v>
       </c>
       <c r="L322" s="5" t="n">
-        <v>36.58422</v>
+        <v>3e-08</v>
       </c>
       <c r="M322" t="inlineStr">
         <is>
@@ -37954,17 +37960,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Reclassification adjustment for realized (loss) gain on sale</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Interest and other income</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -37972,30 +37978,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F323" s="5" t="n">
-        <v>-0.007639</v>
-      </c>
-      <c r="G323" s="5" t="n">
-        <v>-0.002527</v>
-      </c>
-      <c r="H323" s="5" t="n">
-        <v>-0.000133</v>
-      </c>
-      <c r="I323" s="5" t="n">
-        <v>-0.010061</v>
-      </c>
-      <c r="J323" s="5" t="n">
-        <v>-8.000000000000001e-05</v>
-      </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K323" s="5" t="n">
+        <v>21.590573</v>
+      </c>
+      <c r="L323" s="5" t="n">
+        <v>36.58422</v>
       </c>
       <c r="M323" t="inlineStr">
         <is>
@@ -38051,42 +38063,38 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt 11</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
+          <t>Interest and other income</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K324" s="5" t="n">
-        <v>0.842776</v>
+      <c r="F324" s="5" t="n">
+        <v>-0.007639</v>
+      </c>
+      <c r="G324" s="5" t="n">
+        <v>-0.002527</v>
+      </c>
+      <c r="H324" s="5" t="n">
+        <v>-0.000133</v>
+      </c>
+      <c r="I324" s="5" t="n">
+        <v>-0.010061</v>
+      </c>
+      <c r="J324" s="5" t="n">
+        <v>-8.000000000000001e-05</v>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -38147,7 +38155,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Realized gain on sale of marketable securities 6</t>
+          <t>Loss on settlement of debt 11</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -38176,11 +38184,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J325" s="5" t="n">
-        <v>-0.003394</v>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K325" s="5" t="n">
-        <v>-0.016892</v>
+        <v>0.842776</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -38236,12 +38246,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Reclassification adjustment for realized gain on sale of</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Reclassification adjustment for realized gain on sale of marketable securities included in net loss 6</t>
+          <t>Realized gain on sale of marketable securities 6</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -38270,13 +38280,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J326" s="5" t="n">
+        <v>-0.003394</v>
       </c>
       <c r="K326" s="5" t="n">
-        <v>0.016892</v>
+        <v>-0.016892</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -38337,7 +38345,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Unrealized gain on fair value of marketable securities 6</t>
+          <t>Reclassification adjustment for realized gain on sale of marketable securities included in net loss 6</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -38366,11 +38374,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J327" s="5" t="n">
-        <v>-0.01777</v>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K327" s="5" t="n">
-        <v>-0.031622</v>
+        <v>0.016892</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -38426,19 +38436,15 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Reclassification adjustment for realized gain on sale of</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Consulting $</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Unrealized gain on fair value of marketable securities 6</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -38459,16 +38465,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I328" s="5" t="n">
-        <v>0.093</v>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J328" s="5" t="n">
-        <v>0.07275</v>
-      </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.01777</v>
+      </c>
+      <c r="K328" s="5" t="n">
+        <v>-0.031622</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -38529,10 +38535,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Exploration and evaluation, net of recoveries 7(f)</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>Consulting $</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -38554,10 +38564,10 @@
         </is>
       </c>
       <c r="I329" s="5" t="n">
-        <v>-0.098069</v>
+        <v>0.093</v>
       </c>
       <c r="J329" s="5" t="n">
-        <v>-0.268845</v>
+        <v>0.07275</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
@@ -38623,14 +38633,10 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation, net of recoveries 7(f)</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -38641,17 +38647,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G330" s="5" t="n">
-        <v>0.143826</v>
-      </c>
-      <c r="H330" s="5" t="n">
-        <v>0.085725</v>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I330" s="5" t="n">
-        <v>0.000171</v>
+        <v>-0.098069</v>
       </c>
       <c r="J330" s="5" t="n">
-        <v>0.002211</v>
+        <v>-0.268845</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
@@ -38717,7 +38727,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Investor relations</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -38736,16 +38746,16 @@
         </is>
       </c>
       <c r="G331" s="5" t="n">
-        <v>0.095052</v>
+        <v>0.143826</v>
       </c>
       <c r="H331" s="5" t="n">
-        <v>0.094196</v>
+        <v>0.085725</v>
       </c>
       <c r="I331" s="5" t="n">
-        <v>0.062997</v>
+        <v>0.000171</v>
       </c>
       <c r="J331" s="5" t="n">
-        <v>0.043618</v>
+        <v>0.002211</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
@@ -38811,12 +38821,12 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -38830,16 +38840,16 @@
         </is>
       </c>
       <c r="G332" s="5" t="n">
-        <v>0.150487</v>
+        <v>0.095052</v>
       </c>
       <c r="H332" s="5" t="n">
-        <v>0.177265</v>
+        <v>0.094196</v>
       </c>
       <c r="I332" s="5" t="n">
-        <v>0.126529</v>
+        <v>0.062997</v>
       </c>
       <c r="J332" s="5" t="n">
-        <v>0.024592</v>
+        <v>0.043618</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
@@ -38905,10 +38915,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Share-based payments 11(e)</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -38919,23 +38933,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G333" s="5" t="n">
+        <v>0.150487</v>
+      </c>
+      <c r="H333" s="5" t="n">
+        <v>0.177265</v>
+      </c>
+      <c r="I333" s="5" t="n">
+        <v>0.126529</v>
       </c>
       <c r="J333" s="5" t="n">
-        <v>0.051735</v>
+        <v>0.024592</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
@@ -38996,12 +39004,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Reclassification adjustment for realized loss on sale of</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Reclassification adjustment for realized loss on sale of marketable securities included in net loss 6</t>
+          <t>Share-based payments 11(e)</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -39025,13 +39033,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I334" s="5" t="n">
-        <v>-0.017244</v>
-      </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J334" s="5" t="n">
+        <v>0.051735</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
@@ -39097,7 +39105,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Unrealized loss (gain) on fair value of marketable securities 6</t>
+          <t>Reclassification adjustment for realized loss on sale of marketable securities included in net loss 6</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -39122,10 +39130,12 @@
         </is>
       </c>
       <c r="I335" s="5" t="n">
-        <v>-0.016256</v>
-      </c>
-      <c r="J335" s="5" t="n">
-        <v>-0.01777</v>
+        <v>-0.017244</v>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
@@ -39191,14 +39201,10 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Unrealized loss (gain) on fair value of marketable securities 6</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -39214,14 +39220,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H336" s="5" t="n">
-        <v>-8.863339</v>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I336" s="5" t="n">
-        <v>-0.6383180000000001</v>
+        <v>-0.016256</v>
       </c>
       <c r="J336" s="5" t="n">
-        <v>-0.136305</v>
+        <v>-0.01777</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
@@ -39287,12 +39295,12 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -39311,13 +39319,13 @@
         </is>
       </c>
       <c r="H337" s="5" t="n">
-        <v>7.7e-07</v>
+        <v>-8.863339</v>
       </c>
       <c r="I337" s="5" t="n">
-        <v>5e-08</v>
+        <v>-0.6383180000000001</v>
       </c>
       <c r="J337" s="5" t="n">
-        <v>1e-08</v>
+        <v>-0.136305</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
@@ -39383,12 +39391,12 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Loss per share - basic and diluted $</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -39407,13 +39415,13 @@
         </is>
       </c>
       <c r="H338" s="5" t="n">
-        <v>11.474527</v>
+        <v>7.7e-07</v>
       </c>
       <c r="I338" s="5" t="n">
-        <v>11.876829</v>
+        <v>5e-08</v>
       </c>
       <c r="J338" s="5" t="n">
-        <v>11.97021</v>
+        <v>1e-08</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
@@ -39474,15 +39482,19 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Reclassification adjustment for realized loss on sale of</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Administration $</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -39493,21 +39505,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G339" s="5" t="n">
-        <v>0.0985</v>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H339" s="5" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.474527</v>
+      </c>
+      <c r="I339" s="5" t="n">
+        <v>11.876829</v>
+      </c>
+      <c r="J339" s="5" t="n">
+        <v>11.97021</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
@@ -39573,14 +39583,10 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Administration $</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -39592,13 +39598,15 @@
         </is>
       </c>
       <c r="G340" s="5" t="n">
-        <v>0.172611</v>
+        <v>0.0985</v>
       </c>
       <c r="H340" s="5" t="n">
-        <v>0.13828</v>
-      </c>
-      <c r="I340" s="5" t="n">
-        <v>0.093</v>
+        <v>0.126</v>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
@@ -39669,26 +39677,32 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Exploration and evaluation 7(f)</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F341" s="5" t="n">
-        <v>1.206941</v>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G341" s="5" t="n">
-        <v>0.673905</v>
+        <v>0.172611</v>
       </c>
       <c r="H341" s="5" t="n">
-        <v>0.023759</v>
+        <v>0.13828</v>
       </c>
       <c r="I341" s="5" t="n">
-        <v>-0.098069</v>
+        <v>0.093</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
@@ -39759,7 +39773,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
+          <t>Exploration and evaluation 7(f)</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -39768,23 +39782,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F342" s="5" t="n">
+        <v>1.206941</v>
+      </c>
+      <c r="G342" s="5" t="n">
+        <v>0.673905</v>
       </c>
       <c r="H342" s="5" t="n">
-        <v>0.000993</v>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.023759</v>
+      </c>
+      <c r="I342" s="5" t="n">
+        <v>-0.098069</v>
       </c>
       <c r="J342" t="inlineStr">
         <is>
@@ -39855,7 +39863,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Realized loss on sale of marketable securities 6</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -39874,13 +39882,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I343" s="5" t="n">
-        <v>0.017244</v>
+      <c r="H343" s="5" t="n">
+        <v>0.000993</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
@@ -39946,12 +39954,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Reclassification adjustment for realized loss on sale of</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Reclassification adjustment for realized loss on sale of marketable securities included in net loss</t>
+          <t>Realized loss on sale of marketable securities 6</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -39976,7 +39984,7 @@
         </is>
       </c>
       <c r="I344" s="5" t="n">
-        <v>-0.017244</v>
+        <v>0.017244</v>
       </c>
       <c r="J344" t="inlineStr">
         <is>
@@ -40047,7 +40055,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Unrealized (gain) loss on fair value of marketable securities</t>
+          <t>Reclassification adjustment for realized loss on sale of marketable securities included in net loss</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -40066,11 +40074,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H345" s="5" t="n">
-        <v>0.026</v>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I345" s="5" t="n">
-        <v>-0.016256</v>
+        <v>-0.017244</v>
       </c>
       <c r="J345" t="inlineStr">
         <is>
@@ -40136,12 +40146,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Reclassification adjustment for realized loss on sale of</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Share‐based payments 11(f)</t>
+          <t>Unrealized (gain) loss on fair value of marketable securities</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -40155,16 +40165,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G346" s="5" t="n">
-        <v>0.104481</v>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H346" s="5" t="n">
-        <v>0.000993</v>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.026</v>
+      </c>
+      <c r="I346" s="5" t="n">
+        <v>-0.016256</v>
       </c>
       <c r="J346" t="inlineStr">
         <is>
@@ -40235,27 +40245,25 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Shareholdersʹ communications</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share‐based payments 11(f)</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F347" s="5" t="n">
-        <v>0.038222</v>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G347" s="5" t="n">
-        <v>0.013924</v>
+        <v>0.104481</v>
       </c>
       <c r="H347" s="5" t="n">
-        <v>0.008540000000000001</v>
+        <v>0.000993</v>
       </c>
       <c r="I347" t="inlineStr">
         <is>
@@ -40326,17 +40334,17 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Interest accretion                                        10              41,388                        ‐</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Shareholdersʹ communications</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -40344,16 +40352,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F348" s="5" t="n">
+        <v>0.038222</v>
       </c>
       <c r="G348" s="5" t="n">
-        <v>-0.002527</v>
+        <v>0.013924</v>
       </c>
       <c r="H348" s="5" t="n">
-        <v>-0.000133</v>
+        <v>0.008540000000000001</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>
@@ -40424,15 +40430,19 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Operator fee income                                                           (47,357)                       ‐</t>
+          <t>Interest accretion                                        10              41,388                        ‐</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Operator fee income                                                           (47,357)                       ‐ total</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -40444,10 +40454,10 @@
         </is>
       </c>
       <c r="G349" s="5" t="n">
-        <v>1.719296</v>
+        <v>-0.002527</v>
       </c>
       <c r="H349" s="5" t="n">
-        <v>8.137553</v>
+        <v>-0.000133</v>
       </c>
       <c r="I349" t="inlineStr">
         <is>
@@ -40523,14 +40533,10 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Net Loss for the Year</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Operator fee income                                                           (47,357)                       ‐ total</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -40542,10 +40548,10 @@
         </is>
       </c>
       <c r="G350" s="5" t="n">
-        <v>-3.244691</v>
+        <v>1.719296</v>
       </c>
       <c r="H350" s="5" t="n">
-        <v>-8.837339</v>
+        <v>8.137553</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
@@ -40616,15 +40622,19 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Items not permanently included</t>
+          <t>Operator fee income                                                           (47,357)                       ‐</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Unrealized loss on fair value of marketable securities</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr"/>
+          <t>Net Loss for the Year</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -40636,10 +40646,10 @@
         </is>
       </c>
       <c r="G351" s="5" t="n">
-        <v>0.0025</v>
+        <v>-3.244691</v>
       </c>
       <c r="H351" s="5" t="n">
-        <v>0.026</v>
+        <v>-8.837339</v>
       </c>
       <c r="I351" t="inlineStr">
         <is>
@@ -40715,14 +40725,10 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Unrealized loss on fair value of marketable securities</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -40734,10 +40740,10 @@
         </is>
       </c>
       <c r="G352" s="5" t="n">
-        <v>-3.247191</v>
+        <v>0.0025</v>
       </c>
       <c r="H352" s="5" t="n">
-        <v>-8.863339</v>
+        <v>0.026</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>
@@ -40813,12 +40819,12 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Loss per share ‐ basic and diluted $</t>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -40832,10 +40838,10 @@
         </is>
       </c>
       <c r="G353" s="5" t="n">
-        <v>3e-08</v>
+        <v>-3.247191</v>
       </c>
       <c r="H353" s="5" t="n">
-        <v>8e-08</v>
+        <v>-8.863339</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
@@ -40911,12 +40917,12 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Loss per share ‐ basic and diluted $</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -40930,10 +40936,10 @@
         </is>
       </c>
       <c r="G354" s="5" t="n">
-        <v>109.034693</v>
+        <v>3e-08</v>
       </c>
       <c r="H354" s="5" t="n">
-        <v>114.745268</v>
+        <v>8e-08</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
@@ -41004,30 +41010,34 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Items not permanently included</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Share‐based payments 10(e)</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F355" s="5" t="n">
-        <v>0.720066</v>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G355" s="5" t="n">
-        <v>0.104481</v>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>109.034693</v>
+      </c>
+      <c r="H355" s="5" t="n">
+        <v>114.745268</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
@@ -41098,12 +41108,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Other Comprehensive Loss</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Unrealized loss on fair value of marketable securities</t>
+          <t>Share‐based payments 10(e)</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
@@ -41113,10 +41123,10 @@
         </is>
       </c>
       <c r="F356" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.720066</v>
       </c>
       <c r="G356" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.104481</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
@@ -41197,86 +41207,180 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
+          <t>Unrealized loss on fair value of marketable securities</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F357" s="5" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G357" s="5" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Loss</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
           <t>Loss per share ‐ basic and diluted $</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
+      <c r="D358" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F357" s="5" t="n">
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F358" s="5" t="n">
         <v>5.999999999999999e-08</v>
       </c>
-      <c r="G357" s="5" t="n">
+      <c r="G358" s="5" t="n">
         <v>3e-08</v>
       </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T357" t="inlineStr">
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
         <is>
           <t>-</t>
         </is>
